--- a/merged_data.xlsx
+++ b/merged_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F284"/>
+  <dimension ref="A1:F286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,12 +440,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -455,12 +455,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>CPI</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>YoY_Inflation</t>
         </is>
       </c>
     </row>
@@ -469,19 +469,19 @@
         <v>37257</v>
       </c>
       <c r="B2" t="n">
-        <v>57.5419611558503</v>
+        <v>2002</v>
       </c>
       <c r="C2" t="n">
-        <v>58.5030522514953</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>19.42</v>
       </c>
       <c r="E2" t="n">
-        <v>2002</v>
+        <v>57.54196116</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4.943861624</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +489,19 @@
         <v>37288</v>
       </c>
       <c r="B3" t="n">
-        <v>57.418720985315</v>
+        <v>2002</v>
       </c>
       <c r="C3" t="n">
-        <v>58.7136796788145</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>20.28</v>
       </c>
       <c r="E3" t="n">
-        <v>2002</v>
+        <v>57.41872099</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5.191865173</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
         <v>37316</v>
       </c>
       <c r="B4" t="n">
-        <v>57.6651444812884</v>
+        <v>2002</v>
       </c>
       <c r="C4" t="n">
-        <v>59.0659026784627</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>23.7</v>
       </c>
       <c r="E4" t="n">
-        <v>2002</v>
+        <v>57.66514448</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>5.168520874</v>
       </c>
     </row>
     <row r="5">
@@ -529,19 +529,19 @@
         <v>37347</v>
       </c>
       <c r="B5" t="n">
-        <v>57.7883846518237</v>
+        <v>2002</v>
       </c>
       <c r="C5" t="n">
-        <v>59.5385300763497</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>25.73</v>
       </c>
       <c r="E5" t="n">
-        <v>2002</v>
+        <v>57.78838465</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>4.68751786</v>
       </c>
     </row>
     <row r="6">
@@ -549,19 +549,19 @@
         <v>37377</v>
       </c>
       <c r="B6" t="n">
-        <v>58.1580483183325</v>
+        <v>2002</v>
       </c>
       <c r="C6" t="n">
-        <v>59.6634295721229</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>25.35</v>
       </c>
       <c r="E6" t="n">
-        <v>2002</v>
+        <v>58.15804832</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4.656367874</v>
       </c>
     </row>
     <row r="7">
@@ -569,19 +569,19 @@
         <v>37408</v>
       </c>
       <c r="B7" t="n">
-        <v>58.6508953102794</v>
+        <v>2002</v>
       </c>
       <c r="C7" t="n">
-        <v>59.9138707204597</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>24.08</v>
       </c>
       <c r="E7" t="n">
-        <v>2002</v>
+        <v>58.65089531</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4.157562179</v>
       </c>
     </row>
     <row r="8">
@@ -589,19 +589,19 @@
         <v>37438</v>
       </c>
       <c r="B8" t="n">
-        <v>59.2669824727617</v>
+        <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>60.6269858364292</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>25.74</v>
       </c>
       <c r="E8" t="n">
-        <v>2002</v>
+        <v>59.26698247</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>3.88775075</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +609,19 @@
         <v>37469</v>
       </c>
       <c r="B9" t="n">
-        <v>59.6365892941733</v>
+        <v>2002</v>
       </c>
       <c r="C9" t="n">
-        <v>61.0209490274669</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>26.65</v>
       </c>
       <c r="E9" t="n">
-        <v>2002</v>
+        <v>59.63658929</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>3.862622279</v>
       </c>
     </row>
     <row r="10">
@@ -629,19 +629,19 @@
         <v>37500</v>
       </c>
       <c r="B10" t="n">
-        <v>59.7598294647086</v>
+        <v>2002</v>
       </c>
       <c r="C10" t="n">
-        <v>61.4601842722423</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>28.4</v>
       </c>
       <c r="E10" t="n">
-        <v>2002</v>
+        <v>59.75982946</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>4.301018728</v>
       </c>
     </row>
     <row r="11">
@@ -649,19 +649,19 @@
         <v>37530</v>
       </c>
       <c r="B11" t="n">
-        <v>60.0062529606821</v>
+        <v>2002</v>
       </c>
       <c r="C11" t="n">
-        <v>62.265448887664</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>27.54</v>
       </c>
       <c r="E11" t="n">
-        <v>2002</v>
+        <v>60.00625296</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>4.059832851</v>
       </c>
     </row>
     <row r="12">
@@ -669,19 +669,19 @@
         <v>37561</v>
       </c>
       <c r="B12" t="n">
-        <v>60.2526764566555</v>
+        <v>2002</v>
       </c>
       <c r="C12" t="n">
-        <v>64.1460050489577</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>24.34</v>
       </c>
       <c r="E12" t="n">
-        <v>2002</v>
+        <v>60.25267646</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>3.601613532</v>
       </c>
     </row>
     <row r="13">
@@ -689,19 +689,19 @@
         <v>37591</v>
       </c>
       <c r="B13" t="n">
-        <v>59.6365892941733</v>
+        <v>2002</v>
       </c>
       <c r="C13" t="n">
-        <v>65.49292891725671</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>28.33</v>
       </c>
       <c r="E13" t="n">
-        <v>2002</v>
+        <v>59.63658929</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>3.198228595</v>
       </c>
     </row>
     <row r="14">
@@ -709,19 +709,19 @@
         <v>37622</v>
       </c>
       <c r="B14" t="n">
-        <v>59.5134059687352</v>
+        <v>2003</v>
       </c>
       <c r="C14" t="n">
-        <v>66.9666787517007</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>31.18</v>
       </c>
       <c r="E14" t="n">
-        <v>2003</v>
+        <v>59.51340597</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>3.426099447</v>
       </c>
     </row>
     <row r="15">
@@ -729,19 +729,19 @@
         <v>37653</v>
       </c>
       <c r="B15" t="n">
-        <v>59.6365892941733</v>
+        <v>2003</v>
       </c>
       <c r="C15" t="n">
-        <v>68.01821049632029</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>32.77</v>
       </c>
       <c r="E15" t="n">
-        <v>2003</v>
+        <v>59.63658929</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>3.862622279</v>
       </c>
     </row>
     <row r="16">
@@ -749,19 +749,19 @@
         <v>37681</v>
       </c>
       <c r="B16" t="n">
-        <v>60.0062529606821</v>
+        <v>2003</v>
       </c>
       <c r="C16" t="n">
-        <v>68.85494079448171</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>30.61</v>
       </c>
       <c r="E16" t="n">
-        <v>2003</v>
+        <v>60.00625296</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>4.059832851</v>
       </c>
     </row>
     <row r="17">
@@ -769,19 +769,19 @@
         <v>37712</v>
       </c>
       <c r="B17" t="n">
-        <v>60.7455802936996</v>
+        <v>2003</v>
       </c>
       <c r="C17" t="n">
-        <v>69.5227838567134</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>2003</v>
+        <v>60.74558029</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5.117283793</v>
       </c>
     </row>
     <row r="18">
@@ -789,19 +789,19 @@
         <v>37742</v>
       </c>
       <c r="B18" t="n">
-        <v>60.8687636191378</v>
+        <v>2003</v>
       </c>
       <c r="C18" t="n">
-        <v>69.9469284169095</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>25.86</v>
       </c>
       <c r="E18" t="n">
-        <v>2003</v>
+        <v>60.86876362</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4.660946127</v>
       </c>
     </row>
     <row r="19">
@@ -809,19 +809,19 @@
         <v>37773</v>
       </c>
       <c r="B19" t="n">
-        <v>61.2384272856465</v>
+        <v>2003</v>
       </c>
       <c r="C19" t="n">
-        <v>69.8419357816452</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>27.65</v>
       </c>
       <c r="E19" t="n">
-        <v>2003</v>
+        <v>61.23842729</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>4.411751878</v>
       </c>
     </row>
     <row r="20">
@@ -829,19 +829,19 @@
         <v>37803</v>
       </c>
       <c r="B20" t="n">
-        <v>61.7312742775935</v>
+        <v>2003</v>
       </c>
       <c r="C20" t="n">
-        <v>69.9816048836023</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
         <v>28.35</v>
       </c>
       <c r="E20" t="n">
-        <v>2003</v>
+        <v>61.73127428</v>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>4.157950518</v>
       </c>
     </row>
     <row r="21">
@@ -849,19 +849,19 @@
         <v>37834</v>
       </c>
       <c r="B21" t="n">
-        <v>61.48485078162</v>
+        <v>2003</v>
       </c>
       <c r="C21" t="n">
-        <v>70.2195239745224</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>29.89</v>
       </c>
       <c r="E21" t="n">
-        <v>2003</v>
+        <v>61.48485078</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>3.099207231</v>
       </c>
     </row>
     <row r="22">
@@ -869,19 +869,19 @@
         <v>37865</v>
       </c>
       <c r="B22" t="n">
-        <v>61.48485078162</v>
+        <v>2003</v>
       </c>
       <c r="C22" t="n">
-        <v>70.7672837169105</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>27.11</v>
       </c>
       <c r="E22" t="n">
-        <v>2003</v>
+        <v>61.48485078</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>2.886590093</v>
       </c>
     </row>
     <row r="23">
@@ -889,19 +889,19 @@
         <v>37895</v>
       </c>
       <c r="B23" t="n">
-        <v>61.9776977735669</v>
+        <v>2003</v>
       </c>
       <c r="C23" t="n">
-        <v>70.9724528115095</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
         <v>29.61</v>
       </c>
       <c r="E23" t="n">
-        <v>2003</v>
+        <v>61.97769777</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>3.285398964</v>
       </c>
     </row>
     <row r="24">
@@ -909,19 +909,19 @@
         <v>37926</v>
       </c>
       <c r="B24" t="n">
-        <v>62.1009379441023</v>
+        <v>2003</v>
       </c>
       <c r="C24" t="n">
-        <v>71.2139037647779</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
         <v>28.75</v>
       </c>
       <c r="E24" t="n">
-        <v>2003</v>
+        <v>62.10093794</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>3.067517654</v>
       </c>
     </row>
     <row r="25">
@@ -929,19 +929,19 @@
         <v>37956</v>
       </c>
       <c r="B25" t="n">
-        <v>61.8545144481288</v>
+        <v>2003</v>
       </c>
       <c r="C25" t="n">
-        <v>71.5841071545631</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
         <v>29.81</v>
       </c>
       <c r="E25" t="n">
-        <v>2003</v>
+        <v>61.85451445</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>3.71906774</v>
       </c>
     </row>
     <row r="26">
@@ -949,19 +949,19 @@
         <v>37987</v>
       </c>
       <c r="B26" t="n">
-        <v>62.1009379441023</v>
+        <v>2004</v>
       </c>
       <c r="C26" t="n">
-        <v>72.1280139562075</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>31.28</v>
       </c>
       <c r="E26" t="n">
-        <v>2004</v>
+        <v>62.10093794</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>4.347813628</v>
       </c>
     </row>
     <row r="27">
@@ -969,19 +969,19 @@
         <v>38018</v>
       </c>
       <c r="B27" t="n">
-        <v>62.1009379441023</v>
+        <v>2004</v>
       </c>
       <c r="C27" t="n">
-        <v>72.5678913577736</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>30.86</v>
       </c>
       <c r="E27" t="n">
-        <v>2004</v>
+        <v>62.10093794</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>4.132276307</v>
       </c>
     </row>
     <row r="28">
@@ -989,19 +989,19 @@
         <v>38047</v>
       </c>
       <c r="B28" t="n">
-        <v>62.1009379441023</v>
+        <v>2004</v>
       </c>
       <c r="C28" t="n">
-        <v>72.9088766135861</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>33.63</v>
       </c>
       <c r="E28" t="n">
-        <v>2004</v>
+        <v>62.10093794</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.490777844</v>
       </c>
     </row>
     <row r="29">
@@ -1009,19 +1009,19 @@
         <v>38078</v>
       </c>
       <c r="B29" t="n">
-        <v>62.1009379441023</v>
+        <v>2004</v>
       </c>
       <c r="C29" t="n">
-        <v>73.1785824656412</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>33.59</v>
       </c>
       <c r="E29" t="n">
-        <v>2004</v>
+        <v>62.10093794</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>2.231203725</v>
       </c>
     </row>
     <row r="30">
@@ -1029,19 +1029,19 @@
         <v>38108</v>
       </c>
       <c r="B30" t="n">
-        <v>62.5937849360492</v>
+        <v>2004</v>
       </c>
       <c r="C30" t="n">
-        <v>73.55167556098409</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>37.57</v>
       </c>
       <c r="E30" t="n">
-        <v>2004</v>
+        <v>62.59378494</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2.834000913</v>
       </c>
     </row>
     <row r="31">
@@ -1049,19 +1049,19 @@
         <v>38139</v>
       </c>
       <c r="B31" t="n">
-        <v>63.0866887730933</v>
+        <v>2004</v>
       </c>
       <c r="C31" t="n">
-        <v>74.07374903174789</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
         <v>35.18</v>
       </c>
       <c r="E31" t="n">
-        <v>2004</v>
+        <v>63.08668877</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>3.01814003</v>
       </c>
     </row>
     <row r="32">
@@ -1069,19 +1069,19 @@
         <v>38169</v>
       </c>
       <c r="B32" t="n">
-        <v>63.7027759355755</v>
+        <v>2004</v>
       </c>
       <c r="C32" t="n">
-        <v>74.74769258349041</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
         <v>38.22</v>
       </c>
       <c r="E32" t="n">
-        <v>2004</v>
+        <v>63.70277594</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>3.193683722</v>
       </c>
     </row>
     <row r="33">
@@ -1089,19 +1089,19 @@
         <v>38200</v>
       </c>
       <c r="B33" t="n">
-        <v>64.3188062529606</v>
+        <v>2004</v>
       </c>
       <c r="C33" t="n">
-        <v>75.2633444863481</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
         <v>42.74</v>
       </c>
       <c r="E33" t="n">
-        <v>2004</v>
+        <v>64.31880624999999</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>4.609193054</v>
       </c>
     </row>
     <row r="34">
@@ -1109,19 +1109,19 @@
         <v>38231</v>
       </c>
       <c r="B34" t="n">
-        <v>64.4420464234959</v>
+        <v>2004</v>
       </c>
       <c r="C34" t="n">
-        <v>75.51185916431319</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
         <v>43.2</v>
       </c>
       <c r="E34" t="n">
-        <v>2004</v>
+        <v>64.44204642</v>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>4.809632949</v>
       </c>
     </row>
     <row r="35">
@@ -1129,19 +1129,19 @@
         <v>38261</v>
       </c>
       <c r="B35" t="n">
-        <v>64.81171009000469</v>
+        <v>2004</v>
       </c>
       <c r="C35" t="n">
-        <v>75.8441753034525</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
         <v>49.78</v>
       </c>
       <c r="E35" t="n">
-        <v>2004</v>
+        <v>64.81171009000001</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>4.572632444</v>
       </c>
     </row>
     <row r="36">
@@ -1149,19 +1149,19 @@
         <v>38292</v>
       </c>
       <c r="B36" t="n">
-        <v>64.6884699194694</v>
+        <v>2004</v>
       </c>
       <c r="C36" t="n">
-        <v>76.3675330877975</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
         <v>43.11</v>
       </c>
       <c r="E36" t="n">
-        <v>2004</v>
+        <v>64.68846992</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>4.166655225</v>
       </c>
     </row>
     <row r="37">
@@ -1169,19 +1169,19 @@
         <v>38322</v>
       </c>
       <c r="B37" t="n">
-        <v>64.19562292752239</v>
+        <v>2004</v>
       </c>
       <c r="C37" t="n">
-        <v>77.0241384061935</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
         <v>39.6</v>
       </c>
       <c r="E37" t="n">
-        <v>2004</v>
+        <v>64.19562293</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>3.784862755</v>
       </c>
     </row>
     <row r="38">
@@ -1189,19 +1189,19 @@
         <v>38353</v>
       </c>
       <c r="B38" t="n">
-        <v>64.81171009000469</v>
+        <v>2005</v>
       </c>
       <c r="C38" t="n">
-        <v>77.470758454061</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
         <v>44.51</v>
       </c>
       <c r="E38" t="n">
-        <v>2005</v>
+        <v>64.81171009000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>4.365106608</v>
       </c>
     </row>
     <row r="39">
@@ -1209,19 +1209,19 @@
         <v>38384</v>
       </c>
       <c r="B39" t="n">
-        <v>64.6884699194694</v>
+        <v>2005</v>
       </c>
       <c r="C39" t="n">
-        <v>77.9279740889734</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>45.48</v>
       </c>
       <c r="E39" t="n">
-        <v>2005</v>
+        <v>64.68846992</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>4.166655225</v>
       </c>
     </row>
     <row r="40">
@@ -1229,19 +1229,19 @@
         <v>38412</v>
       </c>
       <c r="B40" t="n">
-        <v>64.6884699194694</v>
+        <v>2005</v>
       </c>
       <c r="C40" t="n">
-        <v>78.4031701140229</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
         <v>53.1</v>
       </c>
       <c r="E40" t="n">
-        <v>2005</v>
+        <v>64.68846992</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4.166655225</v>
       </c>
     </row>
     <row r="41">
@@ -1249,19 +1249,19 @@
         <v>38443</v>
       </c>
       <c r="B41" t="n">
-        <v>65.1813169114163</v>
+        <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>79.08514062564799</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
         <v>51.88</v>
       </c>
       <c r="E41" t="n">
-        <v>2005</v>
+        <v>65.18131691000001</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>4.960277685</v>
       </c>
     </row>
     <row r="42">
@@ -1269,19 +1269,19 @@
         <v>38473</v>
       </c>
       <c r="B42" t="n">
-        <v>64.9348934154428</v>
+        <v>2005</v>
       </c>
       <c r="C42" t="n">
-        <v>79.47268224877951</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>48.65</v>
       </c>
       <c r="E42" t="n">
-        <v>2005</v>
+        <v>64.93489341999999</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>3.740161235</v>
       </c>
     </row>
     <row r="43">
@@ -1289,19 +1289,19 @@
         <v>38504</v>
       </c>
       <c r="B43" t="n">
-        <v>65.1813169114163</v>
+        <v>2005</v>
       </c>
       <c r="C43" t="n">
-        <v>79.45662832901429</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
         <v>54.35</v>
       </c>
       <c r="E43" t="n">
-        <v>2005</v>
+        <v>65.18131691000001</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>3.320237881</v>
       </c>
     </row>
     <row r="44">
@@ -1309,19 +1309,19 @@
         <v>38534</v>
       </c>
       <c r="B44" t="n">
-        <v>66.2903079109426</v>
+        <v>2005</v>
       </c>
       <c r="C44" t="n">
-        <v>79.65537585570731</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
         <v>57.52</v>
       </c>
       <c r="E44" t="n">
-        <v>2005</v>
+        <v>66.29030791</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>4.061882606</v>
       </c>
     </row>
     <row r="45">
@@ -1329,19 +1329,19 @@
         <v>38565</v>
       </c>
       <c r="B45" t="n">
-        <v>66.5367314069161</v>
+        <v>2005</v>
       </c>
       <c r="C45" t="n">
-        <v>79.7908709385255</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
         <v>63.98</v>
       </c>
       <c r="E45" t="n">
-        <v>2005</v>
+        <v>66.53673141</v>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>3.448330719</v>
       </c>
     </row>
     <row r="46">
@@ -1349,19 +1349,19 @@
         <v>38596</v>
       </c>
       <c r="B46" t="n">
-        <v>66.78315490288951</v>
+        <v>2005</v>
       </c>
       <c r="C46" t="n">
-        <v>80.07020914243969</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
         <v>62.91</v>
       </c>
       <c r="E46" t="n">
-        <v>2005</v>
+        <v>66.7831549</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>3.632889719</v>
       </c>
     </row>
     <row r="47">
@@ -1369,19 +1369,19 @@
         <v>38626</v>
       </c>
       <c r="B47" t="n">
-        <v>67.5224253908099</v>
+        <v>2005</v>
       </c>
       <c r="C47" t="n">
-        <v>80.6706257416576</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
         <v>58.54</v>
       </c>
       <c r="E47" t="n">
-        <v>2005</v>
+        <v>67.52242539</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>4.182446809</v>
       </c>
     </row>
     <row r="48">
@@ -1389,19 +1389,19 @@
         <v>38657</v>
       </c>
       <c r="B48" t="n">
-        <v>68.1385125532922</v>
+        <v>2005</v>
       </c>
       <c r="C48" t="n">
-        <v>81.11435608396729</v>
+        <v>11</v>
       </c>
       <c r="D48" t="n">
         <v>55.24</v>
       </c>
       <c r="E48" t="n">
-        <v>2005</v>
+        <v>68.13851255</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>5.333319273</v>
       </c>
     </row>
     <row r="49">
@@ -1409,19 +1409,19 @@
         <v>38687</v>
       </c>
       <c r="B49" t="n">
-        <v>67.76890573188059</v>
+        <v>2005</v>
       </c>
       <c r="C49" t="n">
-        <v>81.4062163452984</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
         <v>56.86</v>
       </c>
       <c r="E49" t="n">
-        <v>2005</v>
+        <v>67.76890573</v>
       </c>
       <c r="F49" t="n">
-        <v>12</v>
+        <v>5.566240565</v>
       </c>
     </row>
     <row r="50">
@@ -1429,19 +1429,19 @@
         <v>38718</v>
       </c>
       <c r="B50" t="n">
-        <v>67.6456655613452</v>
+        <v>2006</v>
       </c>
       <c r="C50" t="n">
-        <v>81.8865496246727</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>62.99</v>
       </c>
       <c r="E50" t="n">
-        <v>2006</v>
+        <v>67.64566556</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>4.372597895</v>
       </c>
     </row>
     <row r="51">
@@ -1449,19 +1449,19 @@
         <v>38749</v>
       </c>
       <c r="B51" t="n">
-        <v>67.6456655613452</v>
+        <v>2006</v>
       </c>
       <c r="C51" t="n">
-        <v>82.2223976261603</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>60.21</v>
       </c>
       <c r="E51" t="n">
-        <v>2006</v>
+        <v>67.64566556</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>4.571441627</v>
       </c>
     </row>
     <row r="52">
@@ -1469,19 +1469,19 @@
         <v>38777</v>
       </c>
       <c r="B52" t="n">
-        <v>67.6456655613452</v>
+        <v>2006</v>
       </c>
       <c r="C52" t="n">
-        <v>82.5759049393897</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>62.06</v>
       </c>
       <c r="E52" t="n">
-        <v>2006</v>
+        <v>67.64566556</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4.571441627</v>
       </c>
     </row>
     <row r="53">
@@ -1489,19 +1489,19 @@
         <v>38808</v>
       </c>
       <c r="B53" t="n">
-        <v>68.214116532449</v>
+        <v>2006</v>
       </c>
       <c r="C53" t="n">
-        <v>82.74928727285371</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>70.26000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>2006</v>
+        <v>68.21411653</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>4.652866442</v>
       </c>
     </row>
     <row r="54">
@@ -1509,19 +1509,19 @@
         <v>38838</v>
       </c>
       <c r="B54" t="n">
-        <v>68.7825675035527</v>
+        <v>2006</v>
       </c>
       <c r="C54" t="n">
-        <v>82.8321254988421</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>69.78</v>
       </c>
       <c r="E54" t="n">
-        <v>2006</v>
+        <v>68.7825675</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>5.925433747</v>
       </c>
     </row>
     <row r="55">
@@ -1529,19 +1529,19 @@
         <v>38869</v>
       </c>
       <c r="B55" t="n">
-        <v>69.9194694457602</v>
+        <v>2006</v>
       </c>
       <c r="C55" t="n">
-        <v>82.65810100858749</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
         <v>68.56</v>
       </c>
       <c r="E55" t="n">
-        <v>2006</v>
+        <v>69.91946944999999</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>7.269188103</v>
       </c>
     </row>
     <row r="56">
@@ -1549,19 +1549,19 @@
         <v>38899</v>
       </c>
       <c r="B56" t="n">
-        <v>70.4879204168639</v>
+        <v>2006</v>
       </c>
       <c r="C56" t="n">
-        <v>82.815108343891</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
         <v>73.67</v>
       </c>
       <c r="E56" t="n">
-        <v>2006</v>
+        <v>70.48792041999999</v>
       </c>
       <c r="F56" t="n">
-        <v>7</v>
+        <v>6.332166252</v>
       </c>
     </row>
     <row r="57">
@@ -1569,19 +1569,19 @@
         <v>38930</v>
       </c>
       <c r="B57" t="n">
-        <v>70.4879204168639</v>
+        <v>2006</v>
       </c>
       <c r="C57" t="n">
-        <v>82.8565274568851</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
         <v>73.23</v>
       </c>
       <c r="E57" t="n">
-        <v>2006</v>
+        <v>70.48792041999999</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>5.938357545</v>
       </c>
     </row>
     <row r="58">
@@ -1589,19 +1589,19 @@
         <v>38961</v>
       </c>
       <c r="B58" t="n">
-        <v>71.0563713879677</v>
+        <v>2006</v>
       </c>
       <c r="C58" t="n">
-        <v>83.0305519471397</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
         <v>61.96</v>
       </c>
       <c r="E58" t="n">
-        <v>2006</v>
+        <v>71.05637139</v>
       </c>
       <c r="F58" t="n">
-        <v>9</v>
+        <v>6.398644226</v>
       </c>
     </row>
     <row r="59">
@@ -1609,19 +1609,19 @@
         <v>38991</v>
       </c>
       <c r="B59" t="n">
-        <v>72.1932733301753</v>
+        <v>2006</v>
       </c>
       <c r="C59" t="n">
-        <v>83.3044318183338</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
         <v>57.81</v>
       </c>
       <c r="E59" t="n">
-        <v>2006</v>
+        <v>72.19327333</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>6.917476546</v>
       </c>
     </row>
     <row r="60">
@@ -1629,19 +1629,19 @@
         <v>39022</v>
       </c>
       <c r="B60" t="n">
-        <v>72.1932733301753</v>
+        <v>2006</v>
       </c>
       <c r="C60" t="n">
-        <v>83.562578848158</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
         <v>58.76</v>
       </c>
       <c r="E60" t="n">
-        <v>2006</v>
+        <v>72.19327333</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>5.950762095</v>
       </c>
     </row>
     <row r="61">
@@ -1649,19 +1649,19 @@
         <v>39052</v>
       </c>
       <c r="B61" t="n">
-        <v>72.1932733301753</v>
+        <v>2006</v>
       </c>
       <c r="C61" t="n">
-        <v>83.9636057638923</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>62.47</v>
       </c>
       <c r="E61" t="n">
-        <v>2006</v>
+        <v>72.19327333</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>6.528610062</v>
       </c>
     </row>
     <row r="62">
@@ -1669,19 +1669,19 @@
         <v>39083</v>
       </c>
       <c r="B62" t="n">
-        <v>72.1932733301753</v>
+        <v>2007</v>
       </c>
       <c r="C62" t="n">
-        <v>84.3331669968868</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
         <v>53.68</v>
       </c>
       <c r="E62" t="n">
-        <v>2007</v>
+        <v>72.19327333</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>6.722689076</v>
       </c>
     </row>
     <row r="63">
@@ -1689,19 +1689,19 @@
         <v>39114</v>
       </c>
       <c r="B63" t="n">
-        <v>72.761724301279</v>
+        <v>2007</v>
       </c>
       <c r="C63" t="n">
-        <v>84.7043336218579</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
         <v>57.56</v>
       </c>
       <c r="E63" t="n">
-        <v>2007</v>
+        <v>72.7617243</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>7.56302521</v>
       </c>
     </row>
     <row r="64">
@@ -1709,19 +1709,19 @@
         <v>39142</v>
       </c>
       <c r="B64" t="n">
-        <v>72.1932733301753</v>
+        <v>2007</v>
       </c>
       <c r="C64" t="n">
-        <v>85.0177061356743</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>62.05</v>
       </c>
       <c r="E64" t="n">
-        <v>2007</v>
+        <v>72.19327333</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>6.722689076</v>
       </c>
     </row>
     <row r="65">
@@ -1729,19 +1729,19 @@
         <v>39173</v>
       </c>
       <c r="B65" t="n">
-        <v>72.761724301279</v>
+        <v>2007</v>
       </c>
       <c r="C65" t="n">
-        <v>85.2302600333654</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
         <v>67.48999999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>2007</v>
+        <v>72.7617243</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>6.666666667</v>
       </c>
     </row>
     <row r="66">
@@ -1749,19 +1749,19 @@
         <v>39203</v>
       </c>
       <c r="B66" t="n">
-        <v>73.3301752723828</v>
+        <v>2007</v>
       </c>
       <c r="C66" t="n">
-        <v>85.468821281076</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
         <v>67.20999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>2007</v>
+        <v>73.33017527</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>6.611570248</v>
       </c>
     </row>
     <row r="67">
@@ -1769,19 +1769,19 @@
         <v>39234</v>
       </c>
       <c r="B67" t="n">
-        <v>73.8986262434865</v>
+        <v>2007</v>
       </c>
       <c r="C67" t="n">
-        <v>85.7080246855772</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
         <v>71.05</v>
       </c>
       <c r="E67" t="n">
-        <v>2007</v>
+        <v>73.89862624</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>5.691056911</v>
       </c>
     </row>
     <row r="68">
@@ -1789,19 +1789,19 @@
         <v>39264</v>
       </c>
       <c r="B68" t="n">
-        <v>75.03552818569401</v>
+        <v>2007</v>
       </c>
       <c r="C68" t="n">
-        <v>85.9138359369669</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
         <v>76.93000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>2007</v>
+        <v>75.03552818999999</v>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>6.451612903</v>
       </c>
     </row>
     <row r="69">
@@ -1809,19 +1809,19 @@
         <v>39295</v>
       </c>
       <c r="B69" t="n">
-        <v>75.60397915679771</v>
+        <v>2007</v>
       </c>
       <c r="C69" t="n">
-        <v>86.317752558259</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
         <v>70.76000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>2007</v>
+        <v>75.60397915999999</v>
       </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>7.258064516</v>
       </c>
     </row>
     <row r="70">
@@ -1829,19 +1829,19 @@
         <v>39326</v>
       </c>
       <c r="B70" t="n">
-        <v>75.60397915679771</v>
+        <v>2007</v>
       </c>
       <c r="C70" t="n">
-        <v>86.4731545015859</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
         <v>77.17</v>
       </c>
       <c r="E70" t="n">
-        <v>2007</v>
+        <v>75.60397915999999</v>
       </c>
       <c r="F70" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="71">
@@ -1849,19 +1849,19 @@
         <v>39356</v>
       </c>
       <c r="B71" t="n">
-        <v>76.17243012790151</v>
+        <v>2007</v>
       </c>
       <c r="C71" t="n">
-        <v>86.73258584499131</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
         <v>82.34</v>
       </c>
       <c r="E71" t="n">
-        <v>2007</v>
+        <v>76.17243013</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>5.511811024</v>
       </c>
     </row>
     <row r="72">
@@ -1869,19 +1869,19 @@
         <v>39387</v>
       </c>
       <c r="B72" t="n">
-        <v>76.17243012790151</v>
+        <v>2007</v>
       </c>
       <c r="C72" t="n">
-        <v>87.06201227857289</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
         <v>92.41</v>
       </c>
       <c r="E72" t="n">
-        <v>2007</v>
+        <v>76.17243013</v>
       </c>
       <c r="F72" t="n">
-        <v>11</v>
+        <v>5.511811024</v>
       </c>
     </row>
     <row r="73">
@@ -1889,19 +1889,19 @@
         <v>39417</v>
       </c>
       <c r="B73" t="n">
-        <v>76.17243012790151</v>
+        <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>87.7064166179474</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
         <v>90.93000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>2007</v>
+        <v>76.17243013</v>
       </c>
       <c r="F73" t="n">
-        <v>12</v>
+        <v>5.511811024</v>
       </c>
     </row>
     <row r="74">
@@ -1909,19 +1909,19 @@
         <v>39448</v>
       </c>
       <c r="B74" t="n">
-        <v>76.17243012790151</v>
+        <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>88.1800072510204</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
         <v>92.18000000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>2008</v>
+        <v>76.17243013</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5.511811024</v>
       </c>
     </row>
     <row r="75">
@@ -1929,19 +1929,19 @@
         <v>39479</v>
       </c>
       <c r="B75" t="n">
-        <v>76.74088109900519</v>
+        <v>2008</v>
       </c>
       <c r="C75" t="n">
-        <v>88.6121787710992</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
         <v>94.98999999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>2008</v>
+        <v>76.7408811</v>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>5.46875</v>
       </c>
     </row>
     <row r="76">
@@ -1949,19 +1949,19 @@
         <v>39508</v>
       </c>
       <c r="B76" t="n">
-        <v>77.87778304121269</v>
+        <v>2008</v>
       </c>
       <c r="C76" t="n">
-        <v>89.0376076448765</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>103.64</v>
       </c>
       <c r="E76" t="n">
-        <v>2008</v>
+        <v>77.87778304</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>7.874015748</v>
       </c>
     </row>
     <row r="77">
@@ -1969,19 +1969,19 @@
         <v>39539</v>
       </c>
       <c r="B77" t="n">
-        <v>78.4462340123164</v>
+        <v>2008</v>
       </c>
       <c r="C77" t="n">
-        <v>89.5272521977147</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>109.07</v>
       </c>
       <c r="E77" t="n">
-        <v>2008</v>
+        <v>78.44623401</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>7.8125</v>
       </c>
     </row>
     <row r="78">
@@ -1989,19 +1989,19 @@
         <v>39569</v>
       </c>
       <c r="B78" t="n">
-        <v>79.0146849834202</v>
+        <v>2008</v>
       </c>
       <c r="C78" t="n">
-        <v>90.23458790256871</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
         <v>122.8</v>
       </c>
       <c r="E78" t="n">
-        <v>2008</v>
+        <v>79.01468498</v>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>7.751937984</v>
       </c>
     </row>
     <row r="79">
@@ -2009,19 +2009,19 @@
         <v>39600</v>
       </c>
       <c r="B79" t="n">
-        <v>79.5831359545239</v>
+        <v>2008</v>
       </c>
       <c r="C79" t="n">
-        <v>90.9024309648004</v>
+        <v>6</v>
       </c>
       <c r="D79" t="n">
         <v>132.32</v>
       </c>
       <c r="E79" t="n">
-        <v>2008</v>
+        <v>79.58313595</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>7.692307692</v>
       </c>
     </row>
     <row r="80">
@@ -2029,19 +2029,19 @@
         <v>39630</v>
       </c>
       <c r="B80" t="n">
-        <v>81.2884888678351</v>
+        <v>2008</v>
       </c>
       <c r="C80" t="n">
-        <v>91.3840485577559</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
         <v>132.72</v>
       </c>
       <c r="E80" t="n">
-        <v>2008</v>
+        <v>81.28848886999999</v>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>8.333333333000001</v>
       </c>
     </row>
     <row r="81">
@@ -2049,19 +2049,19 @@
         <v>39661</v>
       </c>
       <c r="B81" t="n">
-        <v>82.4253908100426</v>
+        <v>2008</v>
       </c>
       <c r="C81" t="n">
-        <v>91.639948038813</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
         <v>113.24</v>
       </c>
       <c r="E81" t="n">
-        <v>2008</v>
+        <v>82.42539081</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>9.022556391</v>
       </c>
     </row>
     <row r="82">
@@ -2069,19 +2069,19 @@
         <v>39692</v>
       </c>
       <c r="B82" t="n">
-        <v>82.9938417811463</v>
+        <v>2008</v>
       </c>
       <c r="C82" t="n">
-        <v>91.87818820812829</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
         <v>97.23</v>
       </c>
       <c r="E82" t="n">
-        <v>2008</v>
+        <v>82.99384178</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>9.77443609</v>
       </c>
     </row>
     <row r="83">
@@ -2089,19 +2089,19 @@
         <v>39722</v>
       </c>
       <c r="B83" t="n">
-        <v>84.1307437233538</v>
+        <v>2008</v>
       </c>
       <c r="C83" t="n">
-        <v>92.2917371812795</v>
+        <v>10</v>
       </c>
       <c r="D83" t="n">
         <v>71.58</v>
       </c>
       <c r="E83" t="n">
-        <v>2008</v>
+        <v>84.13074372</v>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>10.44776119</v>
       </c>
     </row>
     <row r="84">
@@ -2109,19 +2109,19 @@
         <v>39753</v>
       </c>
       <c r="B84" t="n">
-        <v>84.1307437233538</v>
+        <v>2008</v>
       </c>
       <c r="C84" t="n">
-        <v>92.6240533204188</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
         <v>52.45</v>
       </c>
       <c r="E84" t="n">
-        <v>2008</v>
+        <v>84.13074372</v>
       </c>
       <c r="F84" t="n">
-        <v>11</v>
+        <v>10.44776119</v>
       </c>
     </row>
     <row r="85">
@@ -2129,19 +2129,19 @@
         <v>39783</v>
       </c>
       <c r="B85" t="n">
-        <v>83.5622927522501</v>
+        <v>2008</v>
       </c>
       <c r="C85" t="n">
-        <v>92.88348466382421</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
         <v>39.95</v>
       </c>
       <c r="E85" t="n">
-        <v>2008</v>
+        <v>83.56229275</v>
       </c>
       <c r="F85" t="n">
-        <v>12</v>
+        <v>9.701492537</v>
       </c>
     </row>
     <row r="86">
@@ -2149,19 +2149,19 @@
         <v>39814</v>
       </c>
       <c r="B86" t="n">
-        <v>84.1307437233538</v>
+        <v>2009</v>
       </c>
       <c r="C86" t="n">
-        <v>93.3291414765057</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>43.44</v>
       </c>
       <c r="E86" t="n">
-        <v>2009</v>
+        <v>84.13074372</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>10.44776119</v>
       </c>
     </row>
     <row r="87">
@@ -2169,19 +2169,19 @@
         <v>39845</v>
       </c>
       <c r="B87" t="n">
-        <v>84.1307437233538</v>
+        <v>2009</v>
       </c>
       <c r="C87" t="n">
-        <v>93.84254583059629</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>43.32</v>
       </c>
       <c r="E87" t="n">
-        <v>2009</v>
+        <v>84.13074372</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>9.62962963</v>
       </c>
     </row>
     <row r="88">
@@ -2189,19 +2189,19 @@
         <v>39873</v>
       </c>
       <c r="B88" t="n">
-        <v>84.1307437233538</v>
+        <v>2009</v>
       </c>
       <c r="C88" t="n">
-        <v>94.0300556134537</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
         <v>46.54</v>
       </c>
       <c r="E88" t="n">
-        <v>2009</v>
+        <v>84.13074372</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>8.029197079999999</v>
       </c>
     </row>
     <row r="89">
@@ -2209,19 +2209,19 @@
         <v>39904</v>
       </c>
       <c r="B89" t="n">
-        <v>85.2676456655613</v>
+        <v>2009</v>
       </c>
       <c r="C89" t="n">
-        <v>94.4814918372507</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
         <v>50.18</v>
       </c>
       <c r="E89" t="n">
-        <v>2009</v>
+        <v>85.26764566999999</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>8.695652173999999</v>
       </c>
     </row>
     <row r="90">
@@ -2229,19 +2229,19 @@
         <v>39934</v>
       </c>
       <c r="B90" t="n">
-        <v>85.836096636665</v>
+        <v>2009</v>
       </c>
       <c r="C90" t="n">
-        <v>94.9255432579557</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
         <v>57.3</v>
       </c>
       <c r="E90" t="n">
-        <v>2009</v>
+        <v>85.83609663999999</v>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>8.633093525</v>
       </c>
     </row>
     <row r="91">
@@ -2249,19 +2249,19 @@
         <v>39965</v>
       </c>
       <c r="B91" t="n">
-        <v>86.97299857887251</v>
+        <v>2009</v>
       </c>
       <c r="C91" t="n">
-        <v>95.2671706705588</v>
+        <v>6</v>
       </c>
       <c r="D91" t="n">
         <v>68.61</v>
       </c>
       <c r="E91" t="n">
-        <v>2009</v>
+        <v>86.97299858</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>9.285714285999999</v>
       </c>
     </row>
     <row r="92">
@@ -2269,19 +2269,19 @@
         <v>39995</v>
       </c>
       <c r="B92" t="n">
-        <v>90.9521553765987</v>
+        <v>2009</v>
       </c>
       <c r="C92" t="n">
-        <v>95.49577848801501</v>
+        <v>7</v>
       </c>
       <c r="D92" t="n">
         <v>64.44</v>
       </c>
       <c r="E92" t="n">
-        <v>2009</v>
+        <v>90.95215537999999</v>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>11.88811189</v>
       </c>
     </row>
     <row r="93">
@@ -2289,19 +2289,19 @@
         <v>40026</v>
       </c>
       <c r="B93" t="n">
-        <v>92.0890573188063</v>
+        <v>2009</v>
       </c>
       <c r="C93" t="n">
-        <v>95.6389794523205</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
         <v>72.51000000000001</v>
       </c>
       <c r="E93" t="n">
-        <v>2009</v>
+        <v>92.08905731999999</v>
       </c>
       <c r="F93" t="n">
-        <v>8</v>
+        <v>11.72413793</v>
       </c>
     </row>
     <row r="94">
@@ -2309,19 +2309,19 @@
         <v>40057</v>
       </c>
       <c r="B94" t="n">
-        <v>92.65750828991</v>
+        <v>2009</v>
       </c>
       <c r="C94" t="n">
-        <v>95.8685505049626</v>
+        <v>9</v>
       </c>
       <c r="D94" t="n">
         <v>67.65000000000001</v>
       </c>
       <c r="E94" t="n">
-        <v>2009</v>
+        <v>92.65750829</v>
       </c>
       <c r="F94" t="n">
-        <v>9</v>
+        <v>11.64383562</v>
       </c>
     </row>
     <row r="95">
@@ -2329,19 +2329,19 @@
         <v>40087</v>
       </c>
       <c r="B95" t="n">
-        <v>93.7944102321175</v>
+        <v>2009</v>
       </c>
       <c r="C95" t="n">
-        <v>96.1369720434365</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
         <v>72.77</v>
       </c>
       <c r="E95" t="n">
-        <v>2009</v>
+        <v>93.79441023</v>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>11.48648649</v>
       </c>
     </row>
     <row r="96">
@@ -2349,19 +2349,19 @@
         <v>40118</v>
       </c>
       <c r="B96" t="n">
-        <v>95.4997631454287</v>
+        <v>2009</v>
       </c>
       <c r="C96" t="n">
-        <v>96.5312563128694</v>
+        <v>11</v>
       </c>
       <c r="D96" t="n">
         <v>76.66</v>
       </c>
       <c r="E96" t="n">
-        <v>2009</v>
+        <v>95.49976315000001</v>
       </c>
       <c r="F96" t="n">
-        <v>11</v>
+        <v>13.51351351</v>
       </c>
     </row>
     <row r="97">
@@ -2369,19 +2369,19 @@
         <v>40148</v>
       </c>
       <c r="B97" t="n">
-        <v>96.0682141165324</v>
+        <v>2009</v>
       </c>
       <c r="C97" t="n">
-        <v>96.8882954884471</v>
+        <v>12</v>
       </c>
       <c r="D97" t="n">
         <v>74.45999999999999</v>
       </c>
       <c r="E97" t="n">
-        <v>2009</v>
+        <v>96.06821411999999</v>
       </c>
       <c r="F97" t="n">
-        <v>12</v>
+        <v>14.96598639</v>
       </c>
     </row>
     <row r="98">
@@ -2389,19 +2389,19 @@
         <v>40179</v>
       </c>
       <c r="B98" t="n">
-        <v>97.7735670298437</v>
+        <v>2010</v>
       </c>
       <c r="C98" t="n">
-        <v>97.61489589701939</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
         <v>76.17</v>
       </c>
       <c r="E98" t="n">
-        <v>2010</v>
+        <v>97.77356703</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>16.21621622</v>
       </c>
     </row>
     <row r="99">
@@ -2409,19 +2409,19 @@
         <v>40210</v>
       </c>
       <c r="B99" t="n">
-        <v>96.6366650876362</v>
+        <v>2010</v>
       </c>
       <c r="C99" t="n">
-        <v>98.37617277228451</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>73.75</v>
       </c>
       <c r="E99" t="n">
-        <v>2010</v>
+        <v>96.63666508999999</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>14.86486486</v>
       </c>
     </row>
     <row r="100">
@@ -2429,19 +2429,19 @@
         <v>40238</v>
       </c>
       <c r="B100" t="n">
-        <v>96.6366650876362</v>
+        <v>2010</v>
       </c>
       <c r="C100" t="n">
-        <v>98.8876506560032</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
         <v>78.83</v>
       </c>
       <c r="E100" t="n">
-        <v>2010</v>
+        <v>96.63666508999999</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>14.86486486</v>
       </c>
     </row>
     <row r="101">
@@ -2449,19 +2449,19 @@
         <v>40269</v>
       </c>
       <c r="B101" t="n">
-        <v>96.6366650876362</v>
+        <v>2010</v>
       </c>
       <c r="C101" t="n">
-        <v>99.4514643181565</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
         <v>84.81999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>2010</v>
+        <v>96.63666508999999</v>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>13.33333333</v>
       </c>
     </row>
     <row r="102">
@@ -2469,19 +2469,19 @@
         <v>40299</v>
       </c>
       <c r="B102" t="n">
-        <v>97.7735670298437</v>
+        <v>2010</v>
       </c>
       <c r="C102" t="n">
-        <v>99.879140740701</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
         <v>75.95</v>
       </c>
       <c r="E102" t="n">
-        <v>2010</v>
+        <v>97.77356703</v>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>13.90728477</v>
       </c>
     </row>
     <row r="103">
@@ -2489,19 +2489,19 @@
         <v>40330</v>
       </c>
       <c r="B103" t="n">
-        <v>98.91046897205111</v>
+        <v>2010</v>
       </c>
       <c r="C103" t="n">
-        <v>99.879140740701</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
         <v>74.76000000000001</v>
       </c>
       <c r="E103" t="n">
-        <v>2010</v>
+        <v>98.91046897</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>13.7254902</v>
       </c>
     </row>
     <row r="104">
@@ -2509,19 +2509,19 @@
         <v>40360</v>
       </c>
       <c r="B104" t="n">
-        <v>101.184272856466</v>
+        <v>2010</v>
       </c>
       <c r="C104" t="n">
-        <v>99.8890941709555</v>
+        <v>7</v>
       </c>
       <c r="D104" t="n">
         <v>75.58</v>
       </c>
       <c r="E104" t="n">
-        <v>2010</v>
+        <v>101.1842729</v>
       </c>
       <c r="F104" t="n">
-        <v>7</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="105">
@@ -2529,19 +2529,19 @@
         <v>40391</v>
       </c>
       <c r="B105" t="n">
-        <v>101.184272856466</v>
+        <v>2010</v>
       </c>
       <c r="C105" t="n">
-        <v>99.9289078919731</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
         <v>77.04000000000001</v>
       </c>
       <c r="E105" t="n">
-        <v>2010</v>
+        <v>101.1842729</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>9.876543209999999</v>
       </c>
     </row>
     <row r="106">
@@ -2549,19 +2549,19 @@
         <v>40422</v>
       </c>
       <c r="B106" t="n">
-        <v>101.752723827569</v>
+        <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>100.378417645398</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
         <v>77.84</v>
       </c>
       <c r="E106" t="n">
-        <v>2010</v>
+        <v>101.7527238</v>
       </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>9.815950920000001</v>
       </c>
     </row>
     <row r="107">
@@ -2569,19 +2569,19 @@
         <v>40452</v>
       </c>
       <c r="B107" t="n">
-        <v>102.889625769777</v>
+        <v>2010</v>
       </c>
       <c r="C107" t="n">
-        <v>101.131346482385</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
         <v>82.67</v>
       </c>
       <c r="E107" t="n">
-        <v>2010</v>
+        <v>102.8896258</v>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>9.696969697</v>
       </c>
     </row>
     <row r="108">
@@ -2589,19 +2589,19 @@
         <v>40483</v>
       </c>
       <c r="B108" t="n">
-        <v>103.458076740881</v>
+        <v>2010</v>
       </c>
       <c r="C108" t="n">
-        <v>101.970645407709</v>
+        <v>11</v>
       </c>
       <c r="D108" t="n">
         <v>85.28</v>
       </c>
       <c r="E108" t="n">
-        <v>2010</v>
+        <v>103.4580767</v>
       </c>
       <c r="F108" t="n">
-        <v>11</v>
+        <v>8.333333333000001</v>
       </c>
     </row>
     <row r="109">
@@ -2609,19 +2609,19 @@
         <v>40513</v>
       </c>
       <c r="B109" t="n">
-        <v>105.163429654192</v>
+        <v>2010</v>
       </c>
       <c r="C109" t="n">
-        <v>102.613123276712</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
         <v>91.45</v>
       </c>
       <c r="E109" t="n">
-        <v>2010</v>
+        <v>105.1634297</v>
       </c>
       <c r="F109" t="n">
-        <v>12</v>
+        <v>9.467455620999999</v>
       </c>
     </row>
     <row r="110">
@@ -2629,19 +2629,19 @@
         <v>40544</v>
       </c>
       <c r="B110" t="n">
-        <v>106.868782567503</v>
+        <v>2011</v>
       </c>
       <c r="C110" t="n">
-        <v>103.464944259452</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
         <v>96.52</v>
       </c>
       <c r="E110" t="n">
-        <v>2011</v>
+        <v>106.8687826</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>9.302325581</v>
       </c>
     </row>
     <row r="111">
@@ -2649,19 +2649,19 @@
         <v>40575</v>
       </c>
       <c r="B111" t="n">
-        <v>105.163429654192</v>
+        <v>2011</v>
       </c>
       <c r="C111" t="n">
-        <v>104.292684362545</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>103.72</v>
       </c>
       <c r="E111" t="n">
-        <v>2011</v>
+        <v>105.1634297</v>
       </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>8.823529411999999</v>
       </c>
     </row>
     <row r="112">
@@ -2669,19 +2669,19 @@
         <v>40603</v>
       </c>
       <c r="B112" t="n">
-        <v>105.163429654192</v>
+        <v>2011</v>
       </c>
       <c r="C112" t="n">
-        <v>105.116571524894</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
         <v>114.64</v>
       </c>
       <c r="E112" t="n">
-        <v>2011</v>
+        <v>105.1634297</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>8.823529411999999</v>
       </c>
     </row>
     <row r="113">
@@ -2689,19 +2689,19 @@
         <v>40634</v>
       </c>
       <c r="B113" t="n">
-        <v>105.731880625296</v>
+        <v>2011</v>
       </c>
       <c r="C113" t="n">
-        <v>105.926010159455</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>123.26</v>
       </c>
       <c r="E113" t="n">
-        <v>2011</v>
+        <v>105.7318806</v>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>9.411764706</v>
       </c>
     </row>
     <row r="114">
@@ -2709,19 +2709,19 @@
         <v>40664</v>
       </c>
       <c r="B114" t="n">
-        <v>106.300331596399</v>
+        <v>2011</v>
       </c>
       <c r="C114" t="n">
-        <v>106.424002750571</v>
+        <v>5</v>
       </c>
       <c r="D114" t="n">
         <v>114.99</v>
       </c>
       <c r="E114" t="n">
-        <v>2011</v>
+        <v>106.3003316</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>8.720930233000001</v>
       </c>
     </row>
     <row r="115">
@@ -2729,19 +2729,19 @@
         <v>40695</v>
       </c>
       <c r="B115" t="n">
-        <v>107.437233538607</v>
+        <v>2011</v>
       </c>
       <c r="C115" t="n">
-        <v>106.583578713037</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
         <v>113.83</v>
       </c>
       <c r="E115" t="n">
-        <v>2011</v>
+        <v>107.4372335</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>8.620689655</v>
       </c>
     </row>
     <row r="116">
@@ -2749,19 +2749,19 @@
         <v>40725</v>
       </c>
       <c r="B116" t="n">
-        <v>109.711037423022</v>
+        <v>2011</v>
       </c>
       <c r="C116" t="n">
-        <v>106.754071340943</v>
+        <v>7</v>
       </c>
       <c r="D116" t="n">
         <v>116.97</v>
       </c>
       <c r="E116" t="n">
-        <v>2011</v>
+        <v>109.7110374</v>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>8.426966291999999</v>
       </c>
     </row>
     <row r="117">
@@ -2769,19 +2769,19 @@
         <v>40756</v>
       </c>
       <c r="B117" t="n">
-        <v>110.279488394125</v>
+        <v>2011</v>
       </c>
       <c r="C117" t="n">
-        <v>107.148997767167</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
         <v>110.22</v>
       </c>
       <c r="E117" t="n">
-        <v>2011</v>
+        <v>110.2794884</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>8.988764045</v>
       </c>
     </row>
     <row r="118">
@@ -2789,19 +2789,19 @@
         <v>40787</v>
       </c>
       <c r="B118" t="n">
-        <v>111.984841307437</v>
+        <v>2011</v>
       </c>
       <c r="C118" t="n">
-        <v>107.716985448459</v>
+        <v>9</v>
       </c>
       <c r="D118" t="n">
         <v>112.83</v>
       </c>
       <c r="E118" t="n">
-        <v>2011</v>
+        <v>111.9848413</v>
       </c>
       <c r="F118" t="n">
-        <v>9</v>
+        <v>10.05586592</v>
       </c>
     </row>
     <row r="119">
@@ -2809,19 +2809,19 @@
         <v>40817</v>
       </c>
       <c r="B119" t="n">
-        <v>112.553292278541</v>
+        <v>2011</v>
       </c>
       <c r="C119" t="n">
-        <v>108.180301572882</v>
+        <v>10</v>
       </c>
       <c r="D119" t="n">
         <v>109.55</v>
       </c>
       <c r="E119" t="n">
-        <v>2011</v>
+        <v>112.5532923</v>
       </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>9.392265193</v>
       </c>
     </row>
     <row r="120">
@@ -2829,19 +2829,19 @@
         <v>40848</v>
       </c>
       <c r="B120" t="n">
-        <v>113.121743249644</v>
+        <v>2011</v>
       </c>
       <c r="C120" t="n">
-        <v>108.742830921454</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
         <v>110.77</v>
       </c>
       <c r="E120" t="n">
-        <v>2011</v>
+        <v>113.1217432</v>
       </c>
       <c r="F120" t="n">
-        <v>11</v>
+        <v>9.340659341</v>
       </c>
     </row>
     <row r="121">
@@ -2849,19 +2849,19 @@
         <v>40878</v>
       </c>
       <c r="B121" t="n">
-        <v>112.626030089041</v>
+        <v>2011</v>
       </c>
       <c r="C121" t="n">
-        <v>109.286416644704</v>
+        <v>12</v>
       </c>
       <c r="D121" t="n">
         <v>107.87</v>
       </c>
       <c r="E121" t="n">
-        <v>2011</v>
+        <v>112.6260301</v>
       </c>
       <c r="F121" t="n">
-        <v>12</v>
+        <v>7.096193477</v>
       </c>
     </row>
     <row r="122">
@@ -2869,19 +2869,19 @@
         <v>40909</v>
       </c>
       <c r="B122" t="n">
-        <v>113.022600617524</v>
+        <v>2012</v>
       </c>
       <c r="C122" t="n">
-        <v>109.898392066152</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
         <v>110.69</v>
       </c>
       <c r="E122" t="n">
-        <v>2012</v>
+        <v>113.0226006</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>5.758293397</v>
       </c>
     </row>
     <row r="123">
@@ -2889,19 +2889,19 @@
         <v>40940</v>
       </c>
       <c r="B123" t="n">
-        <v>113.617456410248</v>
+        <v>2012</v>
       </c>
       <c r="C123" t="n">
-        <v>110.39285279492</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
         <v>119.33</v>
       </c>
       <c r="E123" t="n">
-        <v>2012</v>
+        <v>113.6174564</v>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>8.038941659000001</v>
       </c>
     </row>
     <row r="124">
@@ -2909,19 +2909,19 @@
         <v>40969</v>
       </c>
       <c r="B124" t="n">
-        <v>114.509740099333</v>
+        <v>2012</v>
       </c>
       <c r="C124" t="n">
-        <v>110.624671396329</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
         <v>125.45</v>
       </c>
       <c r="E124" t="n">
-        <v>2012</v>
+        <v>114.5097401</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>8.887415022000001</v>
       </c>
     </row>
     <row r="125">
@@ -2929,19 +2929,19 @@
         <v>41000</v>
       </c>
       <c r="B125" t="n">
-        <v>116.096022213263</v>
+        <v>2012</v>
       </c>
       <c r="C125" t="n">
-        <v>111.332649257974</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>119.75</v>
       </c>
       <c r="E125" t="n">
-        <v>2012</v>
+        <v>116.0960222</v>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>9.802286241999999</v>
       </c>
     </row>
     <row r="126">
@@ -2949,19 +2949,19 @@
         <v>41030</v>
       </c>
       <c r="B126" t="n">
-        <v>117.18659116659</v>
+        <v>2012</v>
       </c>
       <c r="C126" t="n">
-        <v>111.733355095313</v>
+        <v>5</v>
       </c>
       <c r="D126" t="n">
         <v>110.34</v>
       </c>
       <c r="E126" t="n">
-        <v>2012</v>
+        <v>117.1865912</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>10.24104009</v>
       </c>
     </row>
     <row r="127">
@@ -2969,19 +2969,19 @@
         <v>41061</v>
       </c>
       <c r="B127" t="n">
-        <v>118.574588016279</v>
+        <v>2012</v>
       </c>
       <c r="C127" t="n">
-        <v>111.822614889207</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
         <v>95.16</v>
       </c>
       <c r="E127" t="n">
-        <v>2012</v>
+        <v>118.574588</v>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>10.36638241</v>
       </c>
     </row>
     <row r="128">
@@ -2989,19 +2989,19 @@
         <v>41091</v>
       </c>
       <c r="B128" t="n">
-        <v>120.359155394451</v>
+        <v>2012</v>
       </c>
       <c r="C128" t="n">
-        <v>112.303590325372</v>
+        <v>7</v>
       </c>
       <c r="D128" t="n">
         <v>102.62</v>
       </c>
       <c r="E128" t="n">
-        <v>2012</v>
+        <v>120.3591554</v>
       </c>
       <c r="F128" t="n">
-        <v>7</v>
+        <v>9.705603211</v>
       </c>
     </row>
     <row r="129">
@@ -3009,19 +3009,19 @@
         <v>41122</v>
       </c>
       <c r="B129" t="n">
-        <v>121.84629487626</v>
+        <v>2012</v>
       </c>
       <c r="C129" t="n">
-        <v>112.764016744238</v>
+        <v>8</v>
       </c>
       <c r="D129" t="n">
         <v>113.36</v>
       </c>
       <c r="E129" t="n">
-        <v>2012</v>
+        <v>121.8462949</v>
       </c>
       <c r="F129" t="n">
-        <v>8</v>
+        <v>10.48862907</v>
       </c>
     </row>
     <row r="130">
@@ -3029,19 +3029,19 @@
         <v>41153</v>
       </c>
       <c r="B130" t="n">
-        <v>122.936863829587</v>
+        <v>2012</v>
       </c>
       <c r="C130" t="n">
-        <v>113.406815691636</v>
+        <v>9</v>
       </c>
       <c r="D130" t="n">
         <v>112.86</v>
       </c>
       <c r="E130" t="n">
-        <v>2012</v>
+        <v>122.9368638</v>
       </c>
       <c r="F130" t="n">
-        <v>9</v>
+        <v>9.779915205</v>
       </c>
     </row>
     <row r="131">
@@ -3049,19 +3049,19 @@
         <v>41183</v>
       </c>
       <c r="B131" t="n">
-        <v>123.829147518673</v>
+        <v>2012</v>
       </c>
       <c r="C131" t="n">
-        <v>114.075943067449</v>
+        <v>10</v>
       </c>
       <c r="D131" t="n">
         <v>111.71</v>
       </c>
       <c r="E131" t="n">
-        <v>2012</v>
+        <v>123.8291475</v>
       </c>
       <c r="F131" t="n">
-        <v>10</v>
+        <v>10.01823671</v>
       </c>
     </row>
     <row r="132">
@@ -3069,19 +3069,19 @@
         <v>41214</v>
       </c>
       <c r="B132" t="n">
-        <v>124.324860679276</v>
+        <v>2012</v>
       </c>
       <c r="C132" t="n">
-        <v>114.760482206236</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
         <v>109.06</v>
       </c>
       <c r="E132" t="n">
-        <v>2012</v>
+        <v>124.3248607</v>
       </c>
       <c r="F132" t="n">
-        <v>11</v>
+        <v>9.903593339</v>
       </c>
     </row>
     <row r="133">
@@ -3089,19 +3089,19 @@
         <v>41244</v>
       </c>
       <c r="B133" t="n">
-        <v>124.523145943517</v>
+        <v>2012</v>
       </c>
       <c r="C133" t="n">
-        <v>115.667207594574</v>
+        <v>12</v>
       </c>
       <c r="D133" t="n">
         <v>109.49</v>
       </c>
       <c r="E133" t="n">
-        <v>2012</v>
+        <v>124.5231459</v>
       </c>
       <c r="F133" t="n">
-        <v>12</v>
+        <v>10.56338028</v>
       </c>
     </row>
     <row r="134">
@@ -3109,19 +3109,19 @@
         <v>41275</v>
       </c>
       <c r="B134" t="n">
-        <v>124.721747452199</v>
+        <v>2013</v>
       </c>
       <c r="C134" t="n">
-        <v>116.661908463225</v>
+        <v>1</v>
       </c>
       <c r="D134" t="n">
         <v>112.96</v>
       </c>
       <c r="E134" t="n">
-        <v>2013</v>
+        <v>124.7217475</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>10.351157</v>
       </c>
     </row>
     <row r="135">
@@ -3129,19 +3129,19 @@
         <v>41306</v>
       </c>
       <c r="B135" t="n">
-        <v>125.55640541794</v>
+        <v>2013</v>
       </c>
       <c r="C135" t="n">
-        <v>117.361859364987</v>
+        <v>2</v>
       </c>
       <c r="D135" t="n">
         <v>116.05</v>
       </c>
       <c r="E135" t="n">
-        <v>2013</v>
+        <v>125.5564054</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>10.50802349</v>
       </c>
     </row>
     <row r="136">
@@ -3149,19 +3149,19 @@
         <v>41334</v>
       </c>
       <c r="B136" t="n">
-        <v>125.55640541794</v>
+        <v>2013</v>
       </c>
       <c r="C136" t="n">
-        <v>117.913472048118</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
         <v>108.47</v>
       </c>
       <c r="E136" t="n">
-        <v>2013</v>
+        <v>125.5564054</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>9.646922008000001</v>
       </c>
     </row>
     <row r="137">
@@ -3169,19 +3169,19 @@
         <v>41365</v>
       </c>
       <c r="B137" t="n">
-        <v>126.51030023593</v>
+        <v>2013</v>
       </c>
       <c r="C137" t="n">
-        <v>118.562050406632</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>102.25</v>
       </c>
       <c r="E137" t="n">
-        <v>2013</v>
+        <v>126.5103002</v>
       </c>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>8.970400384</v>
       </c>
     </row>
     <row r="138">
@@ -3189,19 +3189,19 @@
         <v>41395</v>
       </c>
       <c r="B138" t="n">
-        <v>127.46419505392</v>
+        <v>2013</v>
       </c>
       <c r="C138" t="n">
-        <v>119.000643494617</v>
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>102.56</v>
       </c>
       <c r="E138" t="n">
-        <v>2013</v>
+        <v>127.4641951</v>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>8.770290000999999</v>
       </c>
     </row>
     <row r="139">
@@ -3209,19 +3209,19 @@
         <v>41426</v>
       </c>
       <c r="B139" t="n">
-        <v>130.325879507891</v>
+        <v>2013</v>
       </c>
       <c r="C139" t="n">
-        <v>119.31016306769</v>
+        <v>6</v>
       </c>
       <c r="D139" t="n">
         <v>102.92</v>
       </c>
       <c r="E139" t="n">
-        <v>2013</v>
+        <v>130.3258795</v>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>9.910463691</v>
       </c>
     </row>
     <row r="140">
@@ -3229,19 +3229,19 @@
         <v>41456</v>
       </c>
       <c r="B140" t="n">
-        <v>132.352905996119</v>
+        <v>2013</v>
       </c>
       <c r="C140" t="n">
-        <v>119.345802769568</v>
+        <v>7</v>
       </c>
       <c r="D140" t="n">
         <v>107.93</v>
       </c>
       <c r="E140" t="n">
-        <v>2013</v>
+        <v>132.352906</v>
       </c>
       <c r="F140" t="n">
-        <v>7</v>
+        <v>9.964967402999999</v>
       </c>
     </row>
     <row r="141">
@@ -3249,19 +3249,19 @@
         <v>41487</v>
       </c>
       <c r="B141" t="n">
-        <v>134.022221927602</v>
+        <v>2013</v>
       </c>
       <c r="C141" t="n">
-        <v>119.632204698179</v>
+        <v>8</v>
       </c>
       <c r="D141" t="n">
         <v>111.28</v>
       </c>
       <c r="E141" t="n">
-        <v>2013</v>
+        <v>134.0222219</v>
       </c>
       <c r="F141" t="n">
-        <v>8</v>
+        <v>9.992857857000001</v>
       </c>
     </row>
     <row r="142">
@@ -3269,19 +3269,19 @@
         <v>41518</v>
       </c>
       <c r="B142" t="n">
-        <v>135.572301006836</v>
+        <v>2013</v>
       </c>
       <c r="C142" t="n">
-        <v>120.050890925655</v>
+        <v>9</v>
       </c>
       <c r="D142" t="n">
         <v>111.6</v>
       </c>
       <c r="E142" t="n">
-        <v>2013</v>
+        <v>135.572301</v>
       </c>
       <c r="F142" t="n">
-        <v>9</v>
+        <v>10.27798887</v>
       </c>
     </row>
     <row r="143">
@@ -3289,19 +3289,19 @@
         <v>41548</v>
       </c>
       <c r="B143" t="n">
-        <v>136.883906381572</v>
+        <v>2013</v>
       </c>
       <c r="C143" t="n">
-        <v>120.735108986047</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
         <v>109.08</v>
       </c>
       <c r="E143" t="n">
-        <v>2013</v>
+        <v>136.8839064</v>
       </c>
       <c r="F143" t="n">
-        <v>10</v>
+        <v>10.54255733</v>
       </c>
     </row>
     <row r="144">
@@ -3309,19 +3309,19 @@
         <v>41579</v>
       </c>
       <c r="B144" t="n">
-        <v>138.672459165304</v>
+        <v>2013</v>
       </c>
       <c r="C144" t="n">
-        <v>121.387219206909</v>
+        <v>11</v>
       </c>
       <c r="D144" t="n">
         <v>107.79</v>
       </c>
       <c r="E144" t="n">
-        <v>2013</v>
+        <v>138.6724592</v>
       </c>
       <c r="F144" t="n">
-        <v>11</v>
+        <v>11.54040986</v>
       </c>
     </row>
     <row r="145">
@@ -3329,19 +3329,19 @@
         <v>41609</v>
       </c>
       <c r="B145" t="n">
-        <v>136.526195824826</v>
+        <v>2013</v>
       </c>
       <c r="C145" t="n">
-        <v>122.503929865775</v>
+        <v>12</v>
       </c>
       <c r="D145" t="n">
         <v>110.76</v>
       </c>
       <c r="E145" t="n">
-        <v>2013</v>
+        <v>136.5261958</v>
       </c>
       <c r="F145" t="n">
-        <v>12</v>
+        <v>9.639211883</v>
       </c>
     </row>
     <row r="146">
@@ -3349,19 +3349,19 @@
         <v>41640</v>
       </c>
       <c r="B146" t="n">
-        <v>135.453064154587</v>
+        <v>2014</v>
       </c>
       <c r="C146" t="n">
-        <v>123.177552339123</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
         <v>108.12</v>
       </c>
       <c r="E146" t="n">
-        <v>2014</v>
+        <v>135.4530642</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>8.604206501</v>
       </c>
     </row>
     <row r="147">
@@ -3369,19 +3369,19 @@
         <v>41671</v>
       </c>
       <c r="B147" t="n">
-        <v>135.453064154587</v>
+        <v>2014</v>
       </c>
       <c r="C147" t="n">
-        <v>124.027446851491</v>
+        <v>2</v>
       </c>
       <c r="D147" t="n">
         <v>108.9</v>
       </c>
       <c r="E147" t="n">
-        <v>2014</v>
+        <v>135.4530642</v>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>7.882241216</v>
       </c>
     </row>
     <row r="148">
@@ -3389,19 +3389,19 @@
         <v>41699</v>
       </c>
       <c r="B148" t="n">
-        <v>136.16848526808</v>
+        <v>2014</v>
       </c>
       <c r="C148" t="n">
-        <v>125.168559468401</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
         <v>107.48</v>
       </c>
       <c r="E148" t="n">
-        <v>2014</v>
+        <v>136.1684853</v>
       </c>
       <c r="F148" t="n">
-        <v>3</v>
+        <v>8.452041785</v>
       </c>
     </row>
     <row r="149">
@@ -3409,19 +3409,19 @@
         <v>41730</v>
       </c>
       <c r="B149" t="n">
-        <v>137.241616938319</v>
+        <v>2014</v>
       </c>
       <c r="C149" t="n">
-        <v>126.007216236934</v>
+        <v>4</v>
       </c>
       <c r="D149" t="n">
         <v>107.76</v>
       </c>
       <c r="E149" t="n">
-        <v>2014</v>
+        <v>137.2416169</v>
       </c>
       <c r="F149" t="n">
-        <v>4</v>
+        <v>8.482563619</v>
       </c>
     </row>
     <row r="150">
@@ -3429,19 +3429,19 @@
         <v>41760</v>
       </c>
       <c r="B150" t="n">
-        <v>138.07627490406</v>
+        <v>2014</v>
       </c>
       <c r="C150" t="n">
-        <v>126.586762740457</v>
+        <v>5</v>
       </c>
       <c r="D150" t="n">
         <v>109.54</v>
       </c>
       <c r="E150" t="n">
-        <v>2014</v>
+        <v>138.0762749</v>
       </c>
       <c r="F150" t="n">
-        <v>5</v>
+        <v>8.325537885999999</v>
       </c>
     </row>
     <row r="151">
@@ -3449,19 +3449,19 @@
         <v>41791</v>
       </c>
       <c r="B151" t="n">
-        <v>139.149406574299</v>
+        <v>2014</v>
       </c>
       <c r="C151" t="n">
-        <v>127.093103369851</v>
+        <v>6</v>
       </c>
       <c r="D151" t="n">
         <v>111.8</v>
       </c>
       <c r="E151" t="n">
-        <v>2014</v>
+        <v>139.1494066</v>
       </c>
       <c r="F151" t="n">
-        <v>6</v>
+        <v>6.770356816</v>
       </c>
     </row>
     <row r="152">
@@ -3469,19 +3469,19 @@
         <v>41821</v>
       </c>
       <c r="B152" t="n">
-        <v>142.130327880518</v>
+        <v>2014</v>
       </c>
       <c r="C152" t="n">
-        <v>127.105946505663</v>
+        <v>7</v>
       </c>
       <c r="D152" t="n">
         <v>106.77</v>
       </c>
       <c r="E152" t="n">
-        <v>2014</v>
+        <v>142.1303279</v>
       </c>
       <c r="F152" t="n">
-        <v>7</v>
+        <v>7.387387387</v>
       </c>
     </row>
     <row r="153">
@@ -3489,19 +3489,19 @@
         <v>41852</v>
       </c>
       <c r="B153" t="n">
-        <v>143.441933255254</v>
+        <v>2014</v>
       </c>
       <c r="C153" t="n">
-        <v>127.423814117014</v>
+        <v>8</v>
       </c>
       <c r="D153" t="n">
         <v>101.61</v>
       </c>
       <c r="E153" t="n">
-        <v>2014</v>
+        <v>143.4419333</v>
       </c>
       <c r="F153" t="n">
-        <v>8</v>
+        <v>7.028469751</v>
       </c>
     </row>
     <row r="154">
@@ -3509,19 +3509,19 @@
         <v>41883</v>
       </c>
       <c r="B154" t="n">
-        <v>143.203459550756</v>
+        <v>2014</v>
       </c>
       <c r="C154" t="n">
-        <v>128.150093447191</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
         <v>97.09</v>
       </c>
       <c r="E154" t="n">
-        <v>2014</v>
+        <v>143.2034596</v>
       </c>
       <c r="F154" t="n">
-        <v>9</v>
+        <v>5.628847845</v>
       </c>
     </row>
     <row r="155">
@@ -3529,19 +3529,19 @@
         <v>41913</v>
       </c>
       <c r="B155" t="n">
-        <v>143.203459550756</v>
+        <v>2014</v>
       </c>
       <c r="C155" t="n">
-        <v>128.68822083772</v>
+        <v>10</v>
       </c>
       <c r="D155" t="n">
         <v>87.43000000000001</v>
       </c>
       <c r="E155" t="n">
-        <v>2014</v>
+        <v>143.2034596</v>
       </c>
       <c r="F155" t="n">
-        <v>10</v>
+        <v>4.616724739</v>
       </c>
     </row>
     <row r="156">
@@ -3549,19 +3549,19 @@
         <v>41944</v>
       </c>
       <c r="B156" t="n">
-        <v>143.203459550756</v>
+        <v>2014</v>
       </c>
       <c r="C156" t="n">
-        <v>129.344505077721</v>
+        <v>11</v>
       </c>
       <c r="D156" t="n">
         <v>79.44</v>
       </c>
       <c r="E156" t="n">
-        <v>2014</v>
+        <v>143.2034596</v>
       </c>
       <c r="F156" t="n">
-        <v>11</v>
+        <v>3.267411866</v>
       </c>
     </row>
     <row r="157">
@@ -3569,19 +3569,19 @@
         <v>41974</v>
       </c>
       <c r="B157" t="n">
-        <v>142.368801585015</v>
+        <v>2014</v>
       </c>
       <c r="C157" t="n">
-        <v>130.353333395765</v>
+        <v>12</v>
       </c>
       <c r="D157" t="n">
         <v>62.34</v>
       </c>
       <c r="E157" t="n">
-        <v>2014</v>
+        <v>142.3688016</v>
       </c>
       <c r="F157" t="n">
-        <v>12</v>
+        <v>4.279475983</v>
       </c>
     </row>
     <row r="158">
@@ -3589,19 +3589,19 @@
         <v>42005</v>
       </c>
       <c r="B158" t="n">
-        <v>142.488038437264</v>
+        <v>2015</v>
       </c>
       <c r="C158" t="n">
-        <v>131.969642037724</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>47.76</v>
       </c>
       <c r="E158" t="n">
-        <v>2015</v>
+        <v>142.4880384</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>5.193661972</v>
       </c>
     </row>
     <row r="159">
@@ -3609,19 +3609,19 @@
         <v>42036</v>
       </c>
       <c r="B159" t="n">
-        <v>142.726512141761</v>
+        <v>2015</v>
       </c>
       <c r="C159" t="n">
-        <v>133.579529111776</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
         <v>58.1</v>
       </c>
       <c r="E159" t="n">
-        <v>2015</v>
+        <v>142.7265121</v>
       </c>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>5.36971831</v>
       </c>
     </row>
     <row r="160">
@@ -3629,19 +3629,19 @@
         <v>42064</v>
       </c>
       <c r="B160" t="n">
-        <v>143.322696403005</v>
+        <v>2015</v>
       </c>
       <c r="C160" t="n">
-        <v>135.342891658784</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
         <v>55.89</v>
       </c>
       <c r="E160" t="n">
-        <v>2015</v>
+        <v>143.3226964</v>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>5.253940455</v>
       </c>
     </row>
     <row r="161">
@@ -3649,19 +3649,19 @@
         <v>42095</v>
       </c>
       <c r="B161" t="n">
-        <v>143.918880664249</v>
+        <v>2015</v>
       </c>
       <c r="C161" t="n">
-        <v>136.303879295928</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
         <v>59.52</v>
       </c>
       <c r="E161" t="n">
-        <v>2015</v>
+        <v>143.9188807</v>
       </c>
       <c r="F161" t="n">
-        <v>4</v>
+        <v>4.865334492</v>
       </c>
     </row>
     <row r="162">
@@ -3669,19 +3669,19 @@
         <v>42125</v>
       </c>
       <c r="B162" t="n">
-        <v>144.992012334488</v>
+        <v>2015</v>
       </c>
       <c r="C162" t="n">
-        <v>137.312386535577</v>
+        <v>5</v>
       </c>
       <c r="D162" t="n">
         <v>64.08</v>
       </c>
       <c r="E162" t="n">
-        <v>2015</v>
+        <v>144.9920123</v>
       </c>
       <c r="F162" t="n">
-        <v>5</v>
+        <v>5.008635579</v>
       </c>
     </row>
     <row r="163">
@@ -3689,19 +3689,19 @@
         <v>42156</v>
       </c>
       <c r="B163" t="n">
-        <v>146.66132826597</v>
+        <v>2015</v>
       </c>
       <c r="C163" t="n">
-        <v>138.397310433308</v>
+        <v>6</v>
       </c>
       <c r="D163" t="n">
         <v>61.48</v>
       </c>
       <c r="E163" t="n">
-        <v>2015</v>
+        <v>146.6613283</v>
       </c>
       <c r="F163" t="n">
-        <v>6</v>
+        <v>5.398457584</v>
       </c>
     </row>
     <row r="164">
@@ -3709,19 +3709,19 @@
         <v>42186</v>
       </c>
       <c r="B164" t="n">
-        <v>147.376749379463</v>
+        <v>2015</v>
       </c>
       <c r="C164" t="n">
-        <v>139.25523190556</v>
+        <v>7</v>
       </c>
       <c r="D164" t="n">
         <v>56.56</v>
       </c>
       <c r="E164" t="n">
-        <v>2015</v>
+        <v>147.3767494</v>
       </c>
       <c r="F164" t="n">
-        <v>7</v>
+        <v>3.691275168</v>
       </c>
     </row>
     <row r="165">
@@ -3729,19 +3729,19 @@
         <v>42217</v>
       </c>
       <c r="B165" t="n">
-        <v>148.807591606448</v>
+        <v>2015</v>
       </c>
       <c r="C165" t="n">
-        <v>139.561540694679</v>
+        <v>8</v>
       </c>
       <c r="D165" t="n">
         <v>46.52</v>
       </c>
       <c r="E165" t="n">
-        <v>2015</v>
+        <v>148.8075916</v>
       </c>
       <c r="F165" t="n">
-        <v>8</v>
+        <v>3.740648379</v>
       </c>
     </row>
     <row r="166">
@@ -3749,19 +3749,19 @@
         <v>42248</v>
       </c>
       <c r="B166" t="n">
-        <v>149.52301271994</v>
+        <v>2015</v>
       </c>
       <c r="C166" t="n">
-        <v>140.315111688457</v>
+        <v>9</v>
       </c>
       <c r="D166" t="n">
         <v>47.62</v>
       </c>
       <c r="E166" t="n">
-        <v>2015</v>
+        <v>149.5230127</v>
       </c>
       <c r="F166" t="n">
-        <v>9</v>
+        <v>4.412989176</v>
       </c>
     </row>
     <row r="167">
@@ -3769,19 +3769,19 @@
         <v>42278</v>
       </c>
       <c r="B167" t="n">
-        <v>150.357670685682</v>
+        <v>2015</v>
       </c>
       <c r="C167" t="n">
-        <v>141.46553557883</v>
+        <v>10</v>
       </c>
       <c r="D167" t="n">
         <v>48.43</v>
       </c>
       <c r="E167" t="n">
-        <v>2015</v>
+        <v>150.3576707</v>
       </c>
       <c r="F167" t="n">
-        <v>10</v>
+        <v>4.995836803</v>
       </c>
     </row>
     <row r="168">
@@ -3789,19 +3789,19 @@
         <v>42309</v>
       </c>
       <c r="B168" t="n">
-        <v>150.953854946926</v>
+        <v>2015</v>
       </c>
       <c r="C168" t="n">
-        <v>142.894334437932</v>
+        <v>11</v>
       </c>
       <c r="D168" t="n">
         <v>44.27</v>
       </c>
       <c r="E168" t="n">
-        <v>2015</v>
+        <v>150.9538549</v>
       </c>
       <c r="F168" t="n">
-        <v>11</v>
+        <v>5.412156536</v>
       </c>
     </row>
     <row r="169">
@@ -3809,19 +3809,19 @@
         <v>42339</v>
       </c>
       <c r="B169" t="n">
-        <v>150.357670685682</v>
+        <v>2015</v>
       </c>
       <c r="C169" t="n">
-        <v>144.265981342669</v>
+        <v>12</v>
       </c>
       <c r="D169" t="n">
         <v>38.01</v>
       </c>
       <c r="E169" t="n">
-        <v>2015</v>
+        <v>150.3576707</v>
       </c>
       <c r="F169" t="n">
-        <v>12</v>
+        <v>5.611390285</v>
       </c>
     </row>
     <row r="170">
@@ -3829,19 +3829,19 @@
         <v>42370</v>
       </c>
       <c r="B170" t="n">
-        <v>150.596144390179</v>
+        <v>2016</v>
       </c>
       <c r="C170" t="n">
-        <v>146.098054666272</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
         <v>30.7</v>
       </c>
       <c r="E170" t="n">
-        <v>2016</v>
+        <v>150.5961444</v>
       </c>
       <c r="F170" t="n">
-        <v>1</v>
+        <v>5.690376569</v>
       </c>
     </row>
     <row r="171">
@@ -3849,19 +3849,19 @@
         <v>42401</v>
       </c>
       <c r="B171" t="n">
-        <v>150.238433833433</v>
+        <v>2016</v>
       </c>
       <c r="C171" t="n">
-        <v>147.412870695041</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
         <v>32.18</v>
       </c>
       <c r="E171" t="n">
-        <v>2016</v>
+        <v>150.2384338</v>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>5.263157895</v>
       </c>
     </row>
     <row r="172">
@@ -3869,19 +3869,19 @@
         <v>42430</v>
       </c>
       <c r="B172" t="n">
-        <v>150.238433833433</v>
+        <v>2016</v>
       </c>
       <c r="C172" t="n">
-        <v>148.04667944737</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
         <v>38.21</v>
       </c>
       <c r="E172" t="n">
-        <v>2016</v>
+        <v>150.2384338</v>
       </c>
       <c r="F172" t="n">
-        <v>3</v>
+        <v>4.825291181</v>
       </c>
     </row>
     <row r="173">
@@ -3889,19 +3889,19 @@
         <v>42461</v>
       </c>
       <c r="B173" t="n">
-        <v>151.788512912667</v>
+        <v>2016</v>
       </c>
       <c r="C173" t="n">
-        <v>148.949872973359</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>41.58</v>
       </c>
       <c r="E173" t="n">
-        <v>2016</v>
+        <v>151.7885129</v>
       </c>
       <c r="F173" t="n">
-        <v>4</v>
+        <v>5.468102734</v>
       </c>
     </row>
     <row r="174">
@@ -3909,19 +3909,19 @@
         <v>42491</v>
       </c>
       <c r="B174" t="n">
-        <v>153.338591991901</v>
+        <v>2016</v>
       </c>
       <c r="C174" t="n">
-        <v>150.111534607568</v>
+        <v>5</v>
       </c>
       <c r="D174" t="n">
         <v>46.74</v>
       </c>
       <c r="E174" t="n">
-        <v>2016</v>
+        <v>153.338592</v>
       </c>
       <c r="F174" t="n">
-        <v>5</v>
+        <v>5.756578947</v>
       </c>
     </row>
     <row r="175">
@@ -3929,19 +3929,19 @@
         <v>42522</v>
       </c>
       <c r="B175" t="n">
-        <v>155.127144775632</v>
+        <v>2016</v>
       </c>
       <c r="C175" t="n">
-        <v>150.636818862285</v>
+        <v>6</v>
       </c>
       <c r="D175" t="n">
         <v>48.25</v>
       </c>
       <c r="E175" t="n">
-        <v>2016</v>
+        <v>155.1271448</v>
       </c>
       <c r="F175" t="n">
-        <v>6</v>
+        <v>5.772357724</v>
       </c>
     </row>
     <row r="176">
@@ -3949,19 +3949,19 @@
         <v>42552</v>
       </c>
       <c r="B176" t="n">
-        <v>156.31951329812</v>
+        <v>2016</v>
       </c>
       <c r="C176" t="n">
-        <v>151.420250146826</v>
+        <v>7</v>
       </c>
       <c r="D176" t="n">
         <v>44.95</v>
       </c>
       <c r="E176" t="n">
-        <v>2016</v>
+        <v>156.3195133</v>
       </c>
       <c r="F176" t="n">
-        <v>7</v>
+        <v>6.067961165</v>
       </c>
     </row>
     <row r="177">
@@ -3969,19 +3969,19 @@
         <v>42583</v>
       </c>
       <c r="B177" t="n">
-        <v>156.31951329812</v>
+        <v>2016</v>
       </c>
       <c r="C177" t="n">
-        <v>152.086487817081</v>
+        <v>8</v>
       </c>
       <c r="D177" t="n">
         <v>45.84</v>
       </c>
       <c r="E177" t="n">
-        <v>2016</v>
+        <v>156.3195133</v>
       </c>
       <c r="F177" t="n">
-        <v>8</v>
+        <v>5.048076923</v>
       </c>
     </row>
     <row r="178">
@@ -3989,19 +3989,19 @@
         <v>42614</v>
       </c>
       <c r="B178" t="n">
-        <v>156.081039593622</v>
+        <v>2016</v>
       </c>
       <c r="C178" t="n">
-        <v>152.208176528901</v>
+        <v>9</v>
       </c>
       <c r="D178" t="n">
         <v>46.57</v>
       </c>
       <c r="E178" t="n">
-        <v>2016</v>
+        <v>156.0810396</v>
       </c>
       <c r="F178" t="n">
-        <v>9</v>
+        <v>4.385964912</v>
       </c>
     </row>
     <row r="179">
@@ -4009,19 +4009,19 @@
         <v>42644</v>
       </c>
       <c r="B179" t="n">
-        <v>156.677223854866</v>
+        <v>2016</v>
       </c>
       <c r="C179" t="n">
-        <v>152.604066190311</v>
+        <v>10</v>
       </c>
       <c r="D179" t="n">
         <v>49.52</v>
       </c>
       <c r="E179" t="n">
-        <v>2016</v>
+        <v>156.6772239</v>
       </c>
       <c r="F179" t="n">
-        <v>10</v>
+        <v>4.203013481</v>
       </c>
     </row>
     <row r="180">
@@ -4029,19 +4029,19 @@
         <v>42675</v>
       </c>
       <c r="B180" t="n">
-        <v>156.438750150368</v>
+        <v>2016</v>
       </c>
       <c r="C180" t="n">
-        <v>152.878909296691</v>
+        <v>11</v>
       </c>
       <c r="D180" t="n">
         <v>44.73</v>
       </c>
       <c r="E180" t="n">
-        <v>2016</v>
+        <v>156.4387502</v>
       </c>
       <c r="F180" t="n">
-        <v>11</v>
+        <v>3.633491311</v>
       </c>
     </row>
     <row r="181">
@@ -4049,19 +4049,19 @@
         <v>42705</v>
       </c>
       <c r="B181" t="n">
-        <v>155.484855332378</v>
+        <v>2016</v>
       </c>
       <c r="C181" t="n">
-        <v>153.337409245184</v>
+        <v>12</v>
       </c>
       <c r="D181" t="n">
         <v>53.31</v>
       </c>
       <c r="E181" t="n">
-        <v>2016</v>
+        <v>155.4848553</v>
       </c>
       <c r="F181" t="n">
-        <v>12</v>
+        <v>3.40999207</v>
       </c>
     </row>
     <row r="182">
@@ -4069,19 +4069,19 @@
         <v>42736</v>
       </c>
       <c r="B182" t="n">
-        <v>155.36561848013</v>
+        <v>2017</v>
       </c>
       <c r="C182" t="n">
-        <v>153.920166532661</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
         <v>54.58</v>
       </c>
       <c r="E182" t="n">
-        <v>2017</v>
+        <v>155.3656185</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>3.167062549</v>
       </c>
     </row>
     <row r="183">
@@ -4089,19 +4089,19 @@
         <v>42767</v>
       </c>
       <c r="B183" t="n">
-        <v>155.723329036876</v>
+        <v>2017</v>
       </c>
       <c r="C183" t="n">
-        <v>154.428112554031</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
         <v>54.87</v>
       </c>
       <c r="E183" t="n">
-        <v>2017</v>
+        <v>155.723329</v>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3.650793651</v>
       </c>
     </row>
     <row r="184">
@@ -4109,19 +4109,19 @@
         <v>42795</v>
       </c>
       <c r="B184" t="n">
-        <v>155.961802741373</v>
+        <v>2017</v>
       </c>
       <c r="C184" t="n">
-        <v>154.814048785186</v>
+        <v>3</v>
       </c>
       <c r="D184" t="n">
         <v>51.59</v>
       </c>
       <c r="E184" t="n">
-        <v>2017</v>
+        <v>155.9618027</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>3.80952381</v>
       </c>
     </row>
     <row r="185">
@@ -4129,19 +4129,19 @@
         <v>42826</v>
       </c>
       <c r="B185" t="n">
-        <v>156.31951329812</v>
+        <v>2017</v>
       </c>
       <c r="C185" t="n">
-        <v>155.030776702016</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
         <v>52.31</v>
       </c>
       <c r="E185" t="n">
-        <v>2017</v>
+        <v>156.3195133</v>
       </c>
       <c r="F185" t="n">
-        <v>4</v>
+        <v>2.985074627</v>
       </c>
     </row>
     <row r="186">
@@ -4149,19 +4149,19 @@
         <v>42856</v>
       </c>
       <c r="B186" t="n">
-        <v>156.677223854866</v>
+        <v>2017</v>
       </c>
       <c r="C186" t="n">
-        <v>155.511431059786</v>
+        <v>5</v>
       </c>
       <c r="D186" t="n">
         <v>50.33</v>
       </c>
       <c r="E186" t="n">
-        <v>2017</v>
+        <v>156.6772239</v>
       </c>
       <c r="F186" t="n">
-        <v>5</v>
+        <v>2.177293935</v>
       </c>
     </row>
     <row r="187">
@@ -4169,19 +4169,19 @@
         <v>42887</v>
       </c>
       <c r="B187" t="n">
-        <v>157.511881820607</v>
+        <v>2017</v>
       </c>
       <c r="C187" t="n">
-        <v>155.153749727417</v>
+        <v>6</v>
       </c>
       <c r="D187" t="n">
         <v>46.37</v>
       </c>
       <c r="E187" t="n">
-        <v>2017</v>
+        <v>157.5118818</v>
       </c>
       <c r="F187" t="n">
-        <v>6</v>
+        <v>1.537279016</v>
       </c>
     </row>
     <row r="188">
@@ -4189,19 +4189,19 @@
         <v>42917</v>
       </c>
       <c r="B188" t="n">
-        <v>160.015855717831</v>
+        <v>2017</v>
       </c>
       <c r="C188" t="n">
-        <v>155.52620066597</v>
+        <v>7</v>
       </c>
       <c r="D188" t="n">
         <v>48.48</v>
       </c>
       <c r="E188" t="n">
-        <v>2017</v>
+        <v>160.0158557</v>
       </c>
       <c r="F188" t="n">
-        <v>7</v>
+        <v>2.36460717</v>
       </c>
     </row>
     <row r="189">
@@ -4209,19 +4209,19 @@
         <v>42948</v>
       </c>
       <c r="B189" t="n">
-        <v>161.446697944816</v>
+        <v>2017</v>
       </c>
       <c r="C189" t="n">
-        <v>155.821592789649</v>
+        <v>8</v>
       </c>
       <c r="D189" t="n">
         <v>51.7</v>
       </c>
       <c r="E189" t="n">
-        <v>2017</v>
+        <v>161.4466979</v>
       </c>
       <c r="F189" t="n">
-        <v>8</v>
+        <v>3.279938978</v>
       </c>
     </row>
     <row r="190">
@@ -4229,19 +4229,19 @@
         <v>42979</v>
       </c>
       <c r="B190" t="n">
-        <v>161.208224240319</v>
+        <v>2017</v>
       </c>
       <c r="C190" t="n">
-        <v>156.070749624405</v>
+        <v>9</v>
       </c>
       <c r="D190" t="n">
         <v>56.15</v>
       </c>
       <c r="E190" t="n">
-        <v>2017</v>
+        <v>161.2082242</v>
       </c>
       <c r="F190" t="n">
-        <v>9</v>
+        <v>3.284950344</v>
       </c>
     </row>
     <row r="191">
@@ -4249,19 +4249,19 @@
         <v>43009</v>
       </c>
       <c r="B191" t="n">
-        <v>162.281355910557</v>
+        <v>2017</v>
       </c>
       <c r="C191" t="n">
-        <v>156.726391707615</v>
+        <v>10</v>
       </c>
       <c r="D191" t="n">
         <v>57.51</v>
       </c>
       <c r="E191" t="n">
-        <v>2017</v>
+        <v>162.2813559</v>
       </c>
       <c r="F191" t="n">
-        <v>10</v>
+        <v>3.576864536</v>
       </c>
     </row>
     <row r="192">
@@ -4269,19 +4269,19 @@
         <v>43040</v>
       </c>
       <c r="B192" t="n">
-        <v>164.069908694289</v>
+        <v>2017</v>
       </c>
       <c r="C192" t="n">
-        <v>157.165305873995</v>
+        <v>11</v>
       </c>
       <c r="D192" t="n">
         <v>62.71</v>
       </c>
       <c r="E192" t="n">
-        <v>2017</v>
+        <v>164.0699087</v>
       </c>
       <c r="F192" t="n">
-        <v>11</v>
+        <v>4.87804878</v>
       </c>
     </row>
     <row r="193">
@@ -4289,19 +4289,19 @@
         <v>43070</v>
       </c>
       <c r="B193" t="n">
-        <v>163.592961285294</v>
+        <v>2017</v>
       </c>
       <c r="C193" t="n">
-        <v>157.856908737479</v>
+        <v>12</v>
       </c>
       <c r="D193" t="n">
         <v>64.37</v>
       </c>
       <c r="E193" t="n">
-        <v>2017</v>
+        <v>163.5929613</v>
       </c>
       <c r="F193" t="n">
-        <v>12</v>
+        <v>5.214723926</v>
       </c>
     </row>
     <row r="194">
@@ -4309,19 +4309,19 @@
         <v>43101</v>
       </c>
       <c r="B194" t="n">
-        <v>163.235250728547</v>
+        <v>2018</v>
       </c>
       <c r="C194" t="n">
-        <v>158.314766529182</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
         <v>69.08</v>
       </c>
       <c r="E194" t="n">
-        <v>2018</v>
+        <v>163.2352507</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>5.065234075</v>
       </c>
     </row>
     <row r="195">
@@ -4329,19 +4329,19 @@
         <v>43132</v>
       </c>
       <c r="B195" t="n">
-        <v>162.639066467304</v>
+        <v>2018</v>
       </c>
       <c r="C195" t="n">
-        <v>158.821428236971</v>
+        <v>2</v>
       </c>
       <c r="D195" t="n">
         <v>65.31999999999999</v>
       </c>
       <c r="E195" t="n">
-        <v>2018</v>
+        <v>162.6390665</v>
       </c>
       <c r="F195" t="n">
-        <v>2</v>
+        <v>4.441041348</v>
       </c>
     </row>
     <row r="196">
@@ -4349,19 +4349,19 @@
         <v>43160</v>
       </c>
       <c r="B196" t="n">
-        <v>162.758303319552</v>
+        <v>2018</v>
       </c>
       <c r="C196" t="n">
-        <v>158.964308122882</v>
+        <v>3</v>
       </c>
       <c r="D196" t="n">
         <v>66.02</v>
       </c>
       <c r="E196" t="n">
-        <v>2018</v>
+        <v>162.7583033</v>
       </c>
       <c r="F196" t="n">
-        <v>3</v>
+        <v>4.357798165</v>
       </c>
     </row>
     <row r="197">
@@ -4369,19 +4369,19 @@
         <v>43191</v>
       </c>
       <c r="B197" t="n">
-        <v>163.473724433045</v>
+        <v>2018</v>
       </c>
       <c r="C197" t="n">
-        <v>159.313962495367</v>
+        <v>4</v>
       </c>
       <c r="D197" t="n">
         <v>72.11</v>
       </c>
       <c r="E197" t="n">
-        <v>2018</v>
+        <v>163.4737244</v>
       </c>
       <c r="F197" t="n">
-        <v>4</v>
+        <v>4.576659039</v>
       </c>
     </row>
     <row r="198">
@@ -4389,19 +4389,19 @@
         <v>43221</v>
       </c>
       <c r="B198" t="n">
-        <v>164.308382398786</v>
+        <v>2018</v>
       </c>
       <c r="C198" t="n">
-        <v>159.951303110045</v>
+        <v>5</v>
       </c>
       <c r="D198" t="n">
         <v>76.98</v>
       </c>
       <c r="E198" t="n">
-        <v>2018</v>
+        <v>164.3083824</v>
       </c>
       <c r="F198" t="n">
-        <v>5</v>
+        <v>4.870624049</v>
       </c>
     </row>
     <row r="199">
@@ -4409,19 +4409,19 @@
         <v>43252</v>
       </c>
       <c r="B199" t="n">
-        <v>165.143040364528</v>
+        <v>2018</v>
       </c>
       <c r="C199" t="n">
-        <v>161.966712197366</v>
+        <v>6</v>
       </c>
       <c r="D199" t="n">
         <v>74.41</v>
       </c>
       <c r="E199" t="n">
-        <v>2018</v>
+        <v>165.1430404</v>
       </c>
       <c r="F199" t="n">
-        <v>6</v>
+        <v>4.844814534</v>
       </c>
     </row>
     <row r="200">
@@ -4429,19 +4429,19 @@
         <v>43282</v>
       </c>
       <c r="B200" t="n">
-        <v>166.693119443761</v>
+        <v>2018</v>
       </c>
       <c r="C200" t="n">
-        <v>162.501307725547</v>
+        <v>7</v>
       </c>
       <c r="D200" t="n">
         <v>74.25</v>
       </c>
       <c r="E200" t="n">
-        <v>2018</v>
+        <v>166.6931194</v>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>4.172876304</v>
       </c>
     </row>
     <row r="201">
@@ -4449,19 +4449,19 @@
         <v>43313</v>
       </c>
       <c r="B201" t="n">
-        <v>167.408540557254</v>
+        <v>2018</v>
       </c>
       <c r="C201" t="n">
-        <v>162.355217055684</v>
+        <v>8</v>
       </c>
       <c r="D201" t="n">
         <v>72.53</v>
       </c>
       <c r="E201" t="n">
-        <v>2018</v>
+        <v>167.4085406</v>
       </c>
       <c r="F201" t="n">
-        <v>8</v>
+        <v>3.692762186</v>
       </c>
     </row>
     <row r="202">
@@ -4469,19 +4469,19 @@
         <v>43344</v>
       </c>
       <c r="B202" t="n">
-        <v>167.170066852756</v>
+        <v>2018</v>
       </c>
       <c r="C202" t="n">
-        <v>163.134474321086</v>
+        <v>9</v>
       </c>
       <c r="D202" t="n">
         <v>78.89</v>
       </c>
       <c r="E202" t="n">
-        <v>2018</v>
+        <v>167.1700669</v>
       </c>
       <c r="F202" t="n">
-        <v>9</v>
+        <v>3.698224852</v>
       </c>
     </row>
     <row r="203">
@@ -4489,19 +4489,19 @@
         <v>43374</v>
       </c>
       <c r="B203" t="n">
-        <v>167.647014261751</v>
+        <v>2018</v>
       </c>
       <c r="C203" t="n">
-        <v>163.86845953275</v>
+        <v>10</v>
       </c>
       <c r="D203" t="n">
         <v>81.03</v>
       </c>
       <c r="E203" t="n">
-        <v>2018</v>
+        <v>167.6470143</v>
       </c>
       <c r="F203" t="n">
-        <v>10</v>
+        <v>3.306392359</v>
       </c>
     </row>
     <row r="204">
@@ -4509,19 +4509,19 @@
         <v>43405</v>
       </c>
       <c r="B204" t="n">
-        <v>167.885487966249</v>
+        <v>2018</v>
       </c>
       <c r="C204" t="n">
-        <v>163.524263492985</v>
+        <v>11</v>
       </c>
       <c r="D204" t="n">
         <v>64.75</v>
       </c>
       <c r="E204" t="n">
-        <v>2018</v>
+        <v>167.885488</v>
       </c>
       <c r="F204" t="n">
-        <v>11</v>
+        <v>2.325581395</v>
       </c>
     </row>
     <row r="205">
@@ -4529,19 +4529,19 @@
         <v>43435</v>
       </c>
       <c r="B205" t="n">
-        <v>167.050830000508</v>
+        <v>2018</v>
       </c>
       <c r="C205" t="n">
-        <v>163.769567386997</v>
+        <v>12</v>
       </c>
       <c r="D205" t="n">
         <v>57.36</v>
       </c>
       <c r="E205" t="n">
-        <v>2018</v>
+        <v>167.05083</v>
       </c>
       <c r="F205" t="n">
-        <v>12</v>
+        <v>2.113702624</v>
       </c>
     </row>
     <row r="206">
@@ -4549,19 +4549,19 @@
         <v>43466</v>
       </c>
       <c r="B206" t="n">
-        <v>166.454645739264</v>
+        <v>2019</v>
       </c>
       <c r="C206" t="n">
-        <v>164.293567328132</v>
+        <v>1</v>
       </c>
       <c r="D206" t="n">
         <v>59.41</v>
       </c>
       <c r="E206" t="n">
-        <v>2019</v>
+        <v>166.4546457</v>
       </c>
       <c r="F206" t="n">
-        <v>1</v>
+        <v>1.972242513</v>
       </c>
     </row>
     <row r="207">
@@ -4569,19 +4569,19 @@
         <v>43497</v>
       </c>
       <c r="B207" t="n">
-        <v>166.81235629601</v>
+        <v>2019</v>
       </c>
       <c r="C207" t="n">
-        <v>164.9999397978</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
         <v>63.96</v>
       </c>
       <c r="E207" t="n">
-        <v>2019</v>
+        <v>166.8123563</v>
       </c>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>2.565982405</v>
       </c>
     </row>
     <row r="208">
@@ -4589,19 +4589,19 @@
         <v>43525</v>
       </c>
       <c r="B208" t="n">
-        <v>167.408540557254</v>
+        <v>2019</v>
       </c>
       <c r="C208" t="n">
-        <v>166.237375933301</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
         <v>66.14</v>
       </c>
       <c r="E208" t="n">
-        <v>2019</v>
+        <v>167.4085406</v>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>2.857142857</v>
       </c>
     </row>
     <row r="209">
@@ -4609,19 +4609,19 @@
         <v>43556</v>
       </c>
       <c r="B209" t="n">
-        <v>168.362435375244</v>
+        <v>2019</v>
       </c>
       <c r="C209" t="n">
-        <v>167.184878277842</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
         <v>71.23</v>
       </c>
       <c r="E209" t="n">
-        <v>2019</v>
+        <v>168.3624354</v>
       </c>
       <c r="F209" t="n">
-        <v>4</v>
+        <v>2.99051787</v>
       </c>
     </row>
     <row r="210">
@@ -4629,19 +4629,19 @@
         <v>43586</v>
       </c>
       <c r="B210" t="n">
-        <v>169.316330193234</v>
+        <v>2019</v>
       </c>
       <c r="C210" t="n">
-        <v>167.402248351463</v>
+        <v>5</v>
       </c>
       <c r="D210" t="n">
         <v>71.31999999999999</v>
       </c>
       <c r="E210" t="n">
-        <v>2019</v>
+        <v>169.3163302</v>
       </c>
       <c r="F210" t="n">
-        <v>5</v>
+        <v>3.047895501</v>
       </c>
     </row>
     <row r="211">
@@ -4649,19 +4649,19 @@
         <v>43617</v>
       </c>
       <c r="B211" t="n">
-        <v>170.389461863473</v>
+        <v>2019</v>
       </c>
       <c r="C211" t="n">
-        <v>167.418944428018</v>
+        <v>6</v>
       </c>
       <c r="D211" t="n">
         <v>64.22</v>
       </c>
       <c r="E211" t="n">
-        <v>2019</v>
+        <v>170.3894619</v>
       </c>
       <c r="F211" t="n">
-        <v>6</v>
+        <v>3.176895307</v>
       </c>
     </row>
     <row r="212">
@@ -4669,19 +4669,19 @@
         <v>43647</v>
       </c>
       <c r="B212" t="n">
-        <v>171.939540942707</v>
+        <v>2019</v>
       </c>
       <c r="C212" t="n">
-        <v>167.737133117764</v>
+        <v>7</v>
       </c>
       <c r="D212" t="n">
         <v>63.92</v>
       </c>
       <c r="E212" t="n">
-        <v>2019</v>
+        <v>171.9395409</v>
       </c>
       <c r="F212" t="n">
-        <v>7</v>
+        <v>3.147353362</v>
       </c>
     </row>
     <row r="213">
@@ -4689,19 +4689,19 @@
         <v>43678</v>
       </c>
       <c r="B213" t="n">
-        <v>172.893435760697</v>
+        <v>2019</v>
       </c>
       <c r="C213" t="n">
-        <v>167.921753195064</v>
+        <v>8</v>
       </c>
       <c r="D213" t="n">
         <v>59.04</v>
       </c>
       <c r="E213" t="n">
-        <v>2019</v>
+        <v>172.8934358</v>
       </c>
       <c r="F213" t="n">
-        <v>8</v>
+        <v>3.276353276</v>
       </c>
     </row>
     <row r="214">
@@ -4709,19 +4709,19 @@
         <v>43709</v>
       </c>
       <c r="B214" t="n">
-        <v>173.847330578687</v>
+        <v>2019</v>
       </c>
       <c r="C214" t="n">
-        <v>167.854647810446</v>
+        <v>9</v>
       </c>
       <c r="D214" t="n">
         <v>62.83</v>
       </c>
       <c r="E214" t="n">
-        <v>2019</v>
+        <v>173.8473306</v>
       </c>
       <c r="F214" t="n">
-        <v>9</v>
+        <v>3.994293866</v>
       </c>
     </row>
     <row r="215">
@@ -4729,19 +4729,19 @@
         <v>43739</v>
       </c>
       <c r="B215" t="n">
-        <v>175.516646510169</v>
+        <v>2019</v>
       </c>
       <c r="C215" t="n">
-        <v>168.022571811189</v>
+        <v>10</v>
       </c>
       <c r="D215" t="n">
         <v>59.71</v>
       </c>
       <c r="E215" t="n">
-        <v>2019</v>
+        <v>175.5166465</v>
       </c>
       <c r="F215" t="n">
-        <v>10</v>
+        <v>4.694167852</v>
       </c>
     </row>
     <row r="216">
@@ -4749,19 +4749,19 @@
         <v>43770</v>
       </c>
       <c r="B216" t="n">
-        <v>177.185962441652</v>
+        <v>2019</v>
       </c>
       <c r="C216" t="n">
-        <v>168.879530048255</v>
+        <v>11</v>
       </c>
       <c r="D216" t="n">
         <v>63.21</v>
       </c>
       <c r="E216" t="n">
-        <v>2019</v>
+        <v>177.1859624</v>
       </c>
       <c r="F216" t="n">
-        <v>11</v>
+        <v>5.539772727</v>
       </c>
     </row>
     <row r="217">
@@ -4769,19 +4769,19 @@
         <v>43800</v>
       </c>
       <c r="B217" t="n">
-        <v>179.33222578213</v>
+        <v>2019</v>
       </c>
       <c r="C217" t="n">
-        <v>170.821733261447</v>
+        <v>12</v>
       </c>
       <c r="D217" t="n">
         <v>67.31</v>
       </c>
       <c r="E217" t="n">
-        <v>2019</v>
+        <v>179.3322258</v>
       </c>
       <c r="F217" t="n">
-        <v>12</v>
+        <v>7.351891506</v>
       </c>
     </row>
     <row r="218">
@@ -4789,19 +4789,19 @@
         <v>43831</v>
       </c>
       <c r="B218" t="n">
-        <v>179.093752077632</v>
+        <v>2020</v>
       </c>
       <c r="C218" t="n">
-        <v>171.180377829001</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
         <v>63.65</v>
       </c>
       <c r="E218" t="n">
-        <v>2020</v>
+        <v>179.0937521</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>7.593123209</v>
       </c>
     </row>
     <row r="219">
@@ -4809,19 +4809,19 @@
         <v>43862</v>
       </c>
       <c r="B219" t="n">
-        <v>177.782146702896</v>
+        <v>2020</v>
       </c>
       <c r="C219" t="n">
-        <v>171.608375329941</v>
+        <v>2</v>
       </c>
       <c r="D219" t="n">
         <v>55.66</v>
       </c>
       <c r="E219" t="n">
-        <v>2020</v>
+        <v>177.7821467</v>
       </c>
       <c r="F219" t="n">
-        <v>2</v>
+        <v>6.576125804</v>
       </c>
     </row>
     <row r="220">
@@ -4829,19 +4829,19 @@
         <v>43891</v>
       </c>
       <c r="B220" t="n">
-        <v>177.185962441652</v>
+        <v>2020</v>
       </c>
       <c r="C220" t="n">
-        <v>171.728458649785</v>
+        <v>3</v>
       </c>
       <c r="D220" t="n">
         <v>32.01</v>
       </c>
       <c r="E220" t="n">
-        <v>2020</v>
+        <v>177.1859624</v>
       </c>
       <c r="F220" t="n">
-        <v>3</v>
+        <v>5.84045584</v>
       </c>
     </row>
     <row r="221">
@@ -4849,19 +4849,19 @@
         <v>43922</v>
       </c>
       <c r="B221" t="n">
-        <v>180.524594304617</v>
+        <v>2020</v>
       </c>
       <c r="C221" t="n">
-        <v>171.196110670371</v>
+        <v>4</v>
       </c>
       <c r="D221" t="n">
         <v>18.38</v>
       </c>
       <c r="E221" t="n">
-        <v>2020</v>
+        <v>180.5245943</v>
       </c>
       <c r="F221" t="n">
-        <v>4</v>
+        <v>7.223796034</v>
       </c>
     </row>
     <row r="222">
@@ -4869,19 +4869,19 @@
         <v>43952</v>
       </c>
       <c r="B222" t="n">
-        <v>179.928410043373</v>
+        <v>2020</v>
       </c>
       <c r="C222" t="n">
-        <v>170.545605841486</v>
+        <v>5</v>
       </c>
       <c r="D222" t="n">
         <v>29.38</v>
       </c>
       <c r="E222" t="n">
-        <v>2020</v>
+        <v>179.92841</v>
       </c>
       <c r="F222" t="n">
-        <v>5</v>
+        <v>6.267605634</v>
       </c>
     </row>
     <row r="223">
@@ -4889,19 +4889,19 @@
         <v>43983</v>
       </c>
       <c r="B223" t="n">
-        <v>181.001541713612</v>
+        <v>2020</v>
       </c>
       <c r="C223" t="n">
-        <v>170.9890151054</v>
+        <v>6</v>
       </c>
       <c r="D223" t="n">
         <v>40.27</v>
       </c>
       <c r="E223" t="n">
-        <v>2020</v>
+        <v>181.0015417</v>
       </c>
       <c r="F223" t="n">
-        <v>6</v>
+        <v>6.228131561</v>
       </c>
     </row>
     <row r="224">
@@ -4909,19 +4909,19 @@
         <v>44013</v>
       </c>
       <c r="B224" t="n">
-        <v>183.505515610836</v>
+        <v>2020</v>
       </c>
       <c r="C224" t="n">
-        <v>171.604522389197</v>
+        <v>7</v>
       </c>
       <c r="D224" t="n">
         <v>43.24</v>
       </c>
       <c r="E224" t="n">
-        <v>2020</v>
+        <v>183.5055156</v>
       </c>
       <c r="F224" t="n">
-        <v>7</v>
+        <v>6.726768377</v>
       </c>
     </row>
     <row r="225">
@@ -4929,19 +4929,19 @@
         <v>44044</v>
       </c>
       <c r="B225" t="n">
-        <v>184.459410428826</v>
+        <v>2020</v>
       </c>
       <c r="C225" t="n">
-        <v>172.016465970372</v>
+        <v>8</v>
       </c>
       <c r="D225" t="n">
         <v>44.74</v>
       </c>
       <c r="E225" t="n">
-        <v>2020</v>
+        <v>184.4594104</v>
       </c>
       <c r="F225" t="n">
-        <v>8</v>
+        <v>6.689655172</v>
       </c>
     </row>
     <row r="226">
@@ -4949,19 +4949,19 @@
         <v>44075</v>
       </c>
       <c r="B226" t="n">
-        <v>186.486436917055</v>
+        <v>2020</v>
       </c>
       <c r="C226" t="n">
-        <v>173.117443787868</v>
+        <v>9</v>
       </c>
       <c r="D226" t="n">
         <v>40.91</v>
       </c>
       <c r="E226" t="n">
-        <v>2020</v>
+        <v>186.4864369</v>
       </c>
       <c r="F226" t="n">
-        <v>9</v>
+        <v>7.270233196</v>
       </c>
     </row>
     <row r="227">
@@ -4969,19 +4969,19 @@
         <v>44105</v>
       </c>
       <c r="B227" t="n">
-        <v>188.87117396203</v>
+        <v>2020</v>
       </c>
       <c r="C227" t="n">
-        <v>174.606284306892</v>
+        <v>10</v>
       </c>
       <c r="D227" t="n">
         <v>40.19</v>
       </c>
       <c r="E227" t="n">
-        <v>2020</v>
+        <v>188.871174</v>
       </c>
       <c r="F227" t="n">
-        <v>10</v>
+        <v>7.608695652</v>
       </c>
     </row>
     <row r="228">
@@ -4989,19 +4989,19 @@
         <v>44136</v>
       </c>
       <c r="B228" t="n">
-        <v>189.467358223274</v>
+        <v>2020</v>
       </c>
       <c r="C228" t="n">
-        <v>176.160303740161</v>
+        <v>11</v>
       </c>
       <c r="D228" t="n">
         <v>42.69</v>
       </c>
       <c r="E228" t="n">
-        <v>2020</v>
+        <v>189.4673582</v>
       </c>
       <c r="F228" t="n">
-        <v>11</v>
+        <v>6.931359354</v>
       </c>
     </row>
     <row r="229">
@@ -5009,19 +5009,19 @@
         <v>44166</v>
       </c>
       <c r="B229" t="n">
-        <v>187.559568587294</v>
+        <v>2020</v>
       </c>
       <c r="C229" t="n">
-        <v>178.538531414176</v>
+        <v>12</v>
       </c>
       <c r="D229" t="n">
         <v>49.99</v>
       </c>
       <c r="E229" t="n">
-        <v>2020</v>
+        <v>187.5595686</v>
       </c>
       <c r="F229" t="n">
-        <v>12</v>
+        <v>4.587765957</v>
       </c>
     </row>
     <row r="230">
@@ -5029,19 +5029,19 @@
         <v>44197</v>
       </c>
       <c r="B230" t="n">
-        <v>186.367200064806</v>
+        <v>2021</v>
       </c>
       <c r="C230" t="n">
-        <v>178.984830383648</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
         <v>54.77</v>
       </c>
       <c r="E230" t="n">
-        <v>2021</v>
+        <v>186.3672001</v>
       </c>
       <c r="F230" t="n">
-        <v>1</v>
+        <v>4.061251664</v>
       </c>
     </row>
     <row r="231">
@@ -5049,19 +5049,19 @@
         <v>44228</v>
       </c>
       <c r="B231" t="n">
-        <v>186.724910621553</v>
+        <v>2021</v>
       </c>
       <c r="C231" t="n">
-        <v>180.524080210734</v>
+        <v>2</v>
       </c>
       <c r="D231" t="n">
         <v>62.28</v>
       </c>
       <c r="E231" t="n">
-        <v>2021</v>
+        <v>186.7249106</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>5.030181087</v>
       </c>
     </row>
     <row r="232">
@@ -5069,19 +5069,19 @@
         <v>44256</v>
       </c>
       <c r="B232" t="n">
-        <v>186.96338432605</v>
+        <v>2021</v>
       </c>
       <c r="C232" t="n">
-        <v>182.202999139777</v>
+        <v>3</v>
       </c>
       <c r="D232" t="n">
         <v>65.41</v>
       </c>
       <c r="E232" t="n">
-        <v>2021</v>
+        <v>186.9633843</v>
       </c>
       <c r="F232" t="n">
-        <v>3</v>
+        <v>5.518169583</v>
       </c>
     </row>
     <row r="233">
@@ -5089,19 +5089,19 @@
         <v>44287</v>
       </c>
       <c r="B233" t="n">
-        <v>188.155752848538</v>
+        <v>2021</v>
       </c>
       <c r="C233" t="n">
-        <v>182.767776037116</v>
+        <v>4</v>
       </c>
       <c r="D233" t="n">
         <v>64.81</v>
       </c>
       <c r="E233" t="n">
-        <v>2021</v>
+        <v>188.1557528</v>
       </c>
       <c r="F233" t="n">
-        <v>4</v>
+        <v>4.227212682</v>
       </c>
     </row>
     <row r="234">
@@ -5109,19 +5109,19 @@
         <v>44317</v>
       </c>
       <c r="B234" t="n">
-        <v>191.255911007005</v>
+        <v>2021</v>
       </c>
       <c r="C234" t="n">
-        <v>184.284871454926</v>
+        <v>5</v>
       </c>
       <c r="D234" t="n">
         <v>68.53</v>
       </c>
       <c r="E234" t="n">
-        <v>2021</v>
+        <v>191.255911</v>
       </c>
       <c r="F234" t="n">
-        <v>5</v>
+        <v>6.295559973</v>
       </c>
     </row>
     <row r="235">
@@ -5129,19 +5129,19 @@
         <v>44348</v>
       </c>
       <c r="B235" t="n">
-        <v>192.329042677244</v>
+        <v>2021</v>
       </c>
       <c r="C235" t="n">
-        <v>185.26159193344</v>
+        <v>6</v>
       </c>
       <c r="D235" t="n">
         <v>73.16</v>
       </c>
       <c r="E235" t="n">
-        <v>2021</v>
+        <v>192.3290427</v>
       </c>
       <c r="F235" t="n">
-        <v>6</v>
+        <v>6.258234519</v>
       </c>
     </row>
     <row r="236">
@@ -5149,19 +5149,19 @@
         <v>44378</v>
       </c>
       <c r="B236" t="n">
-        <v>193.759884904229</v>
+        <v>2021</v>
       </c>
       <c r="C236" t="n">
-        <v>187.040045165027</v>
+        <v>7</v>
       </c>
       <c r="D236" t="n">
         <v>75.17</v>
       </c>
       <c r="E236" t="n">
-        <v>2021</v>
+        <v>193.7598849</v>
       </c>
       <c r="F236" t="n">
-        <v>7</v>
+        <v>5.588044185</v>
       </c>
     </row>
     <row r="237">
@@ -5169,19 +5169,19 @@
         <v>44409</v>
       </c>
       <c r="B237" t="n">
-        <v>194.236832313224</v>
+        <v>2021</v>
       </c>
       <c r="C237" t="n">
-        <v>188.667270472426</v>
+        <v>8</v>
       </c>
       <c r="D237" t="n">
         <v>70.75</v>
       </c>
       <c r="E237" t="n">
-        <v>2021</v>
+        <v>194.2368323</v>
       </c>
       <c r="F237" t="n">
-        <v>8</v>
+        <v>5.300581771</v>
       </c>
     </row>
     <row r="238">
@@ -5189,19 +5189,19 @@
         <v>44440</v>
       </c>
       <c r="B238" t="n">
-        <v>194.59454286997</v>
+        <v>2021</v>
       </c>
       <c r="C238" t="n">
-        <v>190.855740814816</v>
+        <v>9</v>
       </c>
       <c r="D238" t="n">
         <v>74.48999999999999</v>
       </c>
       <c r="E238" t="n">
-        <v>2021</v>
+        <v>194.5945429</v>
       </c>
       <c r="F238" t="n">
-        <v>9</v>
+        <v>4.347826087</v>
       </c>
     </row>
     <row r="239">
@@ -5209,19 +5209,19 @@
         <v>44470</v>
       </c>
       <c r="B239" t="n">
-        <v>197.336990471692</v>
+        <v>2021</v>
       </c>
       <c r="C239" t="n">
-        <v>193.241353291923</v>
+        <v>10</v>
       </c>
       <c r="D239" t="n">
         <v>83.54000000000001</v>
       </c>
       <c r="E239" t="n">
-        <v>2021</v>
+        <v>197.3369905</v>
       </c>
       <c r="F239" t="n">
-        <v>10</v>
+        <v>4.482323232</v>
       </c>
     </row>
     <row r="240">
@@ -5229,19 +5229,19 @@
         <v>44501</v>
       </c>
       <c r="B240" t="n">
-        <v>198.767832698677</v>
+        <v>2021</v>
       </c>
       <c r="C240" t="n">
-        <v>195.077279556269</v>
+        <v>11</v>
       </c>
       <c r="D240" t="n">
         <v>81.05</v>
       </c>
       <c r="E240" t="n">
-        <v>2021</v>
+        <v>198.7678327</v>
       </c>
       <c r="F240" t="n">
-        <v>11</v>
+        <v>4.90874764</v>
       </c>
     </row>
     <row r="241">
@@ -5249,19 +5249,19 @@
         <v>44531</v>
       </c>
       <c r="B241" t="n">
-        <v>198.052411585184</v>
+        <v>2021</v>
       </c>
       <c r="C241" t="n">
-        <v>196.501262239441</v>
+        <v>12</v>
       </c>
       <c r="D241" t="n">
         <v>74.17</v>
       </c>
       <c r="E241" t="n">
-        <v>2021</v>
+        <v>198.0524116</v>
       </c>
       <c r="F241" t="n">
-        <v>12</v>
+        <v>5.594405594</v>
       </c>
     </row>
     <row r="242">
@@ -5269,19 +5269,19 @@
         <v>44562</v>
       </c>
       <c r="B242" t="n">
-        <v>197.575464176189</v>
+        <v>2022</v>
       </c>
       <c r="C242" t="n">
-        <v>197.56242633592</v>
+        <v>1</v>
       </c>
       <c r="D242" t="n">
         <v>86.51000000000001</v>
       </c>
       <c r="E242" t="n">
-        <v>2022</v>
+        <v>197.5754642</v>
       </c>
       <c r="F242" t="n">
-        <v>1</v>
+        <v>6.014075496</v>
       </c>
     </row>
     <row r="243">
@@ -5289,19 +5289,19 @@
         <v>44593</v>
       </c>
       <c r="B243" t="n">
-        <v>198.052411585184</v>
+        <v>2022</v>
       </c>
       <c r="C243" t="n">
-        <v>199.557928562732</v>
+        <v>2</v>
       </c>
       <c r="D243" t="n">
         <v>97.13</v>
       </c>
       <c r="E243" t="n">
-        <v>2022</v>
+        <v>198.0524116</v>
       </c>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>6.066411239</v>
       </c>
     </row>
     <row r="244">
@@ -5309,19 +5309,19 @@
         <v>44621</v>
       </c>
       <c r="B244" t="n">
-        <v>199.960201221165</v>
+        <v>2022</v>
       </c>
       <c r="C244" t="n">
-        <v>202.790866925045</v>
+        <v>3</v>
       </c>
       <c r="D244" t="n">
         <v>117.25</v>
       </c>
       <c r="E244" t="n">
-        <v>2022</v>
+        <v>199.9602012</v>
       </c>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>6.951530612</v>
       </c>
     </row>
     <row r="245">
@@ -5329,19 +5329,19 @@
         <v>44652</v>
       </c>
       <c r="B245" t="n">
-        <v>202.821885675135</v>
+        <v>2022</v>
       </c>
       <c r="C245" t="n">
-        <v>204.940486781603</v>
+        <v>4</v>
       </c>
       <c r="D245" t="n">
         <v>104.58</v>
       </c>
       <c r="E245" t="n">
-        <v>2022</v>
+        <v>202.8218857</v>
       </c>
       <c r="F245" t="n">
-        <v>4</v>
+        <v>7.794676806</v>
       </c>
     </row>
     <row r="246">
@@ -5349,19 +5349,19 @@
         <v>44682</v>
       </c>
       <c r="B246" t="n">
-        <v>204.729675311115</v>
+        <v>2022</v>
       </c>
       <c r="C246" t="n">
-        <v>205.903721967514</v>
+        <v>5</v>
       </c>
       <c r="D246" t="n">
         <v>113.34</v>
       </c>
       <c r="E246" t="n">
-        <v>2022</v>
+        <v>204.7296753</v>
       </c>
       <c r="F246" t="n">
-        <v>5</v>
+        <v>7.044887781</v>
       </c>
     </row>
     <row r="247">
@@ -5369,19 +5369,19 @@
         <v>44713</v>
       </c>
       <c r="B247" t="n">
-        <v>205.802806981354</v>
+        <v>2022</v>
       </c>
       <c r="C247" t="n">
-        <v>207.283395832134</v>
+        <v>6</v>
       </c>
       <c r="D247" t="n">
         <v>122.71</v>
       </c>
       <c r="E247" t="n">
-        <v>2022</v>
+        <v>205.802807</v>
       </c>
       <c r="F247" t="n">
-        <v>6</v>
+        <v>7.005579665</v>
       </c>
     </row>
     <row r="248">
@@ -5389,19 +5389,19 @@
         <v>44743</v>
       </c>
       <c r="B248" t="n">
-        <v>206.756701799344</v>
+        <v>2022</v>
       </c>
       <c r="C248" t="n">
-        <v>205.873861676751</v>
+        <v>7</v>
       </c>
       <c r="D248" t="n">
         <v>111.93</v>
       </c>
       <c r="E248" t="n">
-        <v>2022</v>
+        <v>206.7567018</v>
       </c>
       <c r="F248" t="n">
-        <v>7</v>
+        <v>6.707692308</v>
       </c>
     </row>
     <row r="249">
@@ -5409,19 +5409,19 @@
         <v>44774</v>
       </c>
       <c r="B249" t="n">
-        <v>207.829833469582</v>
+        <v>2022</v>
       </c>
       <c r="C249" t="n">
-        <v>205.13281274039</v>
+        <v>8</v>
       </c>
       <c r="D249" t="n">
         <v>100.45</v>
       </c>
       <c r="E249" t="n">
-        <v>2022</v>
+        <v>207.8298335</v>
       </c>
       <c r="F249" t="n">
-        <v>8</v>
+        <v>6.998158379</v>
       </c>
     </row>
     <row r="250">
@@ -5429,19 +5429,19 @@
         <v>44805</v>
       </c>
       <c r="B250" t="n">
-        <v>209.02220199207</v>
+        <v>2022</v>
       </c>
       <c r="C250" t="n">
-        <v>204.537854473893</v>
+        <v>9</v>
       </c>
       <c r="D250" t="n">
         <v>89.76000000000001</v>
       </c>
       <c r="E250" t="n">
-        <v>2022</v>
+        <v>209.022202</v>
       </c>
       <c r="F250" t="n">
-        <v>9</v>
+        <v>7.414215686</v>
       </c>
     </row>
     <row r="251">
@@ -5449,19 +5449,19 @@
         <v>44835</v>
       </c>
       <c r="B251" t="n">
-        <v>210.691517923553</v>
+        <v>2022</v>
       </c>
       <c r="C251" t="n">
-        <v>205.744788161839</v>
+        <v>10</v>
       </c>
       <c r="D251" t="n">
         <v>93.33</v>
       </c>
       <c r="E251" t="n">
-        <v>2022</v>
+        <v>210.6915179</v>
       </c>
       <c r="F251" t="n">
-        <v>10</v>
+        <v>6.767371601</v>
       </c>
     </row>
     <row r="252">
@@ -5469,19 +5469,19 @@
         <v>44866</v>
       </c>
       <c r="B252" t="n">
-        <v>210.453044219055</v>
+        <v>2022</v>
       </c>
       <c r="C252" t="n">
-        <v>206.588261106302</v>
+        <v>11</v>
       </c>
       <c r="D252" t="n">
         <v>91.42</v>
       </c>
       <c r="E252" t="n">
-        <v>2022</v>
+        <v>210.4530442</v>
       </c>
       <c r="F252" t="n">
-        <v>11</v>
+        <v>5.878824235</v>
       </c>
     </row>
     <row r="253">
@@ -5489,19 +5489,19 @@
         <v>44896</v>
       </c>
       <c r="B253" t="n">
-        <v>209.499149401065</v>
+        <v>2022</v>
       </c>
       <c r="C253" t="n">
-        <v>207.869042825168</v>
+        <v>12</v>
       </c>
       <c r="D253" t="n">
         <v>80.92</v>
       </c>
       <c r="E253" t="n">
-        <v>2022</v>
+        <v>209.4991494</v>
       </c>
       <c r="F253" t="n">
-        <v>12</v>
+        <v>5.779650813</v>
       </c>
     </row>
     <row r="254">
@@ -5509,19 +5509,19 @@
         <v>44927</v>
       </c>
       <c r="B254" t="n">
-        <v>210.453044219055</v>
+        <v>2023</v>
       </c>
       <c r="C254" t="n">
-        <v>208.970662799455</v>
+        <v>1</v>
       </c>
       <c r="D254" t="n">
         <v>82.5</v>
       </c>
       <c r="E254" t="n">
-        <v>2023</v>
+        <v>210.4530442</v>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>6.517803259</v>
       </c>
     </row>
     <row r="255">
@@ -5529,19 +5529,19 @@
         <v>44958</v>
       </c>
       <c r="B255" t="n">
-        <v>210.810754775801</v>
+        <v>2023</v>
       </c>
       <c r="C255" t="n">
-        <v>210.725998386581</v>
+        <v>2</v>
       </c>
       <c r="D255" t="n">
         <v>82.59</v>
       </c>
       <c r="E255" t="n">
-        <v>2023</v>
+        <v>210.8107548</v>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>6.441902468</v>
       </c>
     </row>
     <row r="256">
@@ -5549,19 +5549,19 @@
         <v>44986</v>
       </c>
       <c r="B256" t="n">
-        <v>211.287702184796</v>
+        <v>2023</v>
       </c>
       <c r="C256" t="n">
-        <v>212.222223708696</v>
+        <v>3</v>
       </c>
       <c r="D256" t="n">
         <v>78.43000000000001</v>
       </c>
       <c r="E256" t="n">
-        <v>2023</v>
+        <v>211.2877022</v>
       </c>
       <c r="F256" t="n">
-        <v>3</v>
+        <v>5.664877758</v>
       </c>
     </row>
     <row r="257">
@@ -5569,19 +5569,19 @@
         <v>45017</v>
       </c>
       <c r="B257" t="n">
-        <v>212.360833855035</v>
+        <v>2023</v>
       </c>
       <c r="C257" t="n">
-        <v>213.51681179856</v>
+        <v>4</v>
       </c>
       <c r="D257" t="n">
         <v>84.64</v>
       </c>
       <c r="E257" t="n">
-        <v>2023</v>
+        <v>212.3608339</v>
       </c>
       <c r="F257" t="n">
-        <v>4</v>
+        <v>4.703115814</v>
       </c>
     </row>
     <row r="258">
@@ -5589,19 +5589,19 @@
         <v>45047</v>
       </c>
       <c r="B258" t="n">
-        <v>213.433965525274</v>
+        <v>2023</v>
       </c>
       <c r="C258" t="n">
-        <v>214.00774066498</v>
+        <v>5</v>
       </c>
       <c r="D258" t="n">
         <v>75.47</v>
       </c>
       <c r="E258" t="n">
-        <v>2023</v>
+        <v>213.4339655</v>
       </c>
       <c r="F258" t="n">
-        <v>5</v>
+        <v>4.251601631</v>
       </c>
     </row>
     <row r="259">
@@ -5609,19 +5609,19 @@
         <v>45078</v>
       </c>
       <c r="B259" t="n">
-        <v>215.818702570249</v>
+        <v>2023</v>
       </c>
       <c r="C259" t="n">
-        <v>213.836605880283</v>
+        <v>6</v>
       </c>
       <c r="D259" t="n">
         <v>74.84</v>
       </c>
       <c r="E259" t="n">
-        <v>2023</v>
+        <v>215.8187026</v>
       </c>
       <c r="F259" t="n">
-        <v>6</v>
+        <v>4.866743917</v>
       </c>
     </row>
     <row r="260">
@@ -5629,19 +5629,19 @@
         <v>45108</v>
       </c>
       <c r="B260" t="n">
-        <v>222.138255739433</v>
+        <v>2023</v>
       </c>
       <c r="C260" t="n">
-        <v>214.09314751813</v>
+        <v>7</v>
       </c>
       <c r="D260" t="n">
         <v>80.11</v>
       </c>
       <c r="E260" t="n">
-        <v>2023</v>
+        <v>222.1382557</v>
       </c>
       <c r="F260" t="n">
-        <v>7</v>
+        <v>7.439446367</v>
       </c>
     </row>
     <row r="261">
@@ -5649,19 +5649,19 @@
         <v>45139</v>
       </c>
       <c r="B261" t="n">
-        <v>222.019018887185</v>
+        <v>2023</v>
       </c>
       <c r="C261" t="n">
-        <v>214.585681776526</v>
+        <v>8</v>
       </c>
       <c r="D261" t="n">
         <v>86.15000000000001</v>
       </c>
       <c r="E261" t="n">
-        <v>2023</v>
+        <v>222.0190189</v>
       </c>
       <c r="F261" t="n">
-        <v>8</v>
+        <v>6.827309237</v>
       </c>
     </row>
     <row r="262">
@@ -5669,19 +5669,19 @@
         <v>45170</v>
       </c>
       <c r="B262" t="n">
-        <v>219.515044989961</v>
+        <v>2023</v>
       </c>
       <c r="C262" t="n">
-        <v>215.143716027564</v>
+        <v>9</v>
       </c>
       <c r="D262" t="n">
         <v>93.72</v>
       </c>
       <c r="E262" t="n">
-        <v>2023</v>
+        <v>219.515045</v>
       </c>
       <c r="F262" t="n">
-        <v>9</v>
+        <v>5.019965773</v>
       </c>
     </row>
     <row r="263">
@@ -5689,19 +5689,19 @@
         <v>45200</v>
       </c>
       <c r="B263" t="n">
-        <v>220.945887216946</v>
+        <v>2023</v>
       </c>
       <c r="C263" t="n">
-        <v>215.660010087212</v>
+        <v>10</v>
       </c>
       <c r="D263" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="E263" t="n">
-        <v>2023</v>
+        <v>220.9458872</v>
       </c>
       <c r="F263" t="n">
-        <v>10</v>
+        <v>4.867006225</v>
       </c>
     </row>
     <row r="264">
@@ -5709,19 +5709,19 @@
         <v>45231</v>
       </c>
       <c r="B264" t="n">
-        <v>222.138255739433</v>
+        <v>2023</v>
       </c>
       <c r="C264" t="n">
-        <v>216.263958548779</v>
+        <v>11</v>
       </c>
       <c r="D264" t="n">
         <v>82.94</v>
       </c>
       <c r="E264" t="n">
-        <v>2023</v>
+        <v>222.1382557</v>
       </c>
       <c r="F264" t="n">
-        <v>11</v>
+        <v>5.552407932</v>
       </c>
     </row>
     <row r="265">
@@ -5729,19 +5729,19 @@
         <v>45261</v>
       </c>
       <c r="B265" t="n">
-        <v>221.422834625941</v>
+        <v>2023</v>
       </c>
       <c r="C265" t="n">
-        <v>217.475066255864</v>
+        <v>12</v>
       </c>
       <c r="D265" t="n">
         <v>77.63</v>
       </c>
       <c r="E265" t="n">
-        <v>2023</v>
+        <v>221.4228346</v>
       </c>
       <c r="F265" t="n">
-        <v>12</v>
+        <v>5.691519636</v>
       </c>
     </row>
     <row r="266">
@@ -5749,19 +5749,19 @@
         <v>45292</v>
       </c>
       <c r="B266" t="n">
-        <v>221.184360921443</v>
+        <v>2024</v>
       </c>
       <c r="C266" t="n">
-        <v>218.388534290503</v>
+        <v>1</v>
       </c>
       <c r="D266" t="n">
         <v>80.12</v>
       </c>
       <c r="E266" t="n">
-        <v>2024</v>
+        <v>221.1843609</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
+        <v>5.099150142</v>
       </c>
     </row>
     <row r="267">
@@ -5769,19 +5769,19 @@
         <v>45323</v>
       </c>
       <c r="B267" t="n">
-        <v>221.542071478189</v>
+        <v>2024</v>
       </c>
       <c r="C267" t="n">
-        <v>220.201021831993</v>
+        <v>2</v>
       </c>
       <c r="D267" t="n">
         <v>83.48</v>
       </c>
       <c r="E267" t="n">
-        <v>2024</v>
+        <v>221.5420715</v>
       </c>
       <c r="F267" t="n">
-        <v>2</v>
+        <v>5.090497738</v>
       </c>
     </row>
     <row r="268">
@@ -5789,19 +5789,19 @@
         <v>45352</v>
       </c>
       <c r="B268" t="n">
-        <v>221.542071478189</v>
+        <v>2024</v>
       </c>
       <c r="C268" t="n">
-        <v>220.553244831641</v>
+        <v>3</v>
       </c>
       <c r="D268" t="n">
         <v>85.41</v>
       </c>
       <c r="E268" t="n">
-        <v>2024</v>
+        <v>221.5420715</v>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>4.853273138</v>
       </c>
     </row>
     <row r="269">
@@ -5809,19 +5809,19 @@
         <v>45383</v>
       </c>
       <c r="B269" t="n">
-        <v>222.615203148428</v>
+        <v>2024</v>
       </c>
       <c r="C269" t="n">
-        <v>221.391259443383</v>
+        <v>4</v>
       </c>
       <c r="D269" t="n">
         <v>89.94</v>
       </c>
       <c r="E269" t="n">
-        <v>2024</v>
+        <v>222.6152031</v>
       </c>
       <c r="F269" t="n">
-        <v>4</v>
+        <v>4.828747894</v>
       </c>
     </row>
     <row r="270">
@@ -5829,19 +5829,19 @@
         <v>45413</v>
       </c>
       <c r="B270" t="n">
-        <v>223.807571670916</v>
+        <v>2024</v>
       </c>
       <c r="C270" t="n">
-        <v>222.409720113287</v>
+        <v>5</v>
       </c>
       <c r="D270" t="n">
         <v>81.75</v>
       </c>
       <c r="E270" t="n">
-        <v>2024</v>
+        <v>223.8075717</v>
       </c>
       <c r="F270" t="n">
-        <v>5</v>
+        <v>4.860335196</v>
       </c>
     </row>
     <row r="271">
@@ -5849,19 +5849,19 @@
         <v>45444</v>
       </c>
       <c r="B271" t="n">
-        <v>226.788492977135</v>
+        <v>2024</v>
       </c>
       <c r="C271" t="n">
-        <v>222.876889178454</v>
+        <v>6</v>
       </c>
       <c r="D271" t="n">
         <v>82.25</v>
       </c>
       <c r="E271" t="n">
-        <v>2024</v>
+        <v>226.788493</v>
       </c>
       <c r="F271" t="n">
-        <v>6</v>
+        <v>5.082872928</v>
       </c>
     </row>
     <row r="272">
@@ -5869,19 +5869,19 @@
         <v>45474</v>
       </c>
       <c r="B272" t="n">
-        <v>230.1271248401</v>
+        <v>2024</v>
       </c>
       <c r="C272" t="n">
-        <v>223.723893985265</v>
+        <v>7</v>
       </c>
       <c r="D272" t="n">
         <v>85.15000000000001</v>
       </c>
       <c r="E272" t="n">
-        <v>2024</v>
+        <v>230.1271248</v>
       </c>
       <c r="F272" t="n">
-        <v>7</v>
+        <v>3.596349973</v>
       </c>
     </row>
     <row r="273">
@@ -5889,19 +5889,19 @@
         <v>45505</v>
       </c>
       <c r="B273" t="n">
-        <v>230.1271248401</v>
+        <v>2024</v>
       </c>
       <c r="C273" t="n">
-        <v>223.679264088317</v>
+        <v>8</v>
       </c>
       <c r="D273" t="n">
         <v>80.36</v>
       </c>
       <c r="E273" t="n">
-        <v>2024</v>
+        <v>230.1271248</v>
       </c>
       <c r="F273" t="n">
-        <v>8</v>
+        <v>3.651987111</v>
       </c>
     </row>
     <row r="274">
@@ -5909,19 +5909,19 @@
         <v>45536</v>
       </c>
       <c r="B274" t="n">
-        <v>231.557967067085</v>
+        <v>2024</v>
       </c>
       <c r="C274" t="n">
-        <v>224.663369369923</v>
+        <v>9</v>
       </c>
       <c r="D274" t="n">
         <v>74.02</v>
       </c>
       <c r="E274" t="n">
-        <v>2024</v>
+        <v>231.5579671</v>
       </c>
       <c r="F274" t="n">
-        <v>9</v>
+        <v>5.486148832</v>
       </c>
     </row>
     <row r="275">
@@ -5929,19 +5929,19 @@
         <v>45566</v>
       </c>
       <c r="B275" t="n">
-        <v>234.658125225553</v>
+        <v>2024</v>
       </c>
       <c r="C275" t="n">
-        <v>225.921354522723</v>
+        <v>10</v>
       </c>
       <c r="D275" t="n">
         <v>75.63</v>
       </c>
       <c r="E275" t="n">
-        <v>2024</v>
+        <v>234.6581252</v>
       </c>
       <c r="F275" t="n">
-        <v>10</v>
+        <v>6.206152186</v>
       </c>
     </row>
     <row r="276">
@@ -5949,19 +5949,19 @@
         <v>45597</v>
       </c>
       <c r="B276" t="n">
-        <v>234.300414668806</v>
+        <v>2024</v>
       </c>
       <c r="C276" t="n">
-        <v>226.802393639437</v>
+        <v>11</v>
       </c>
       <c r="D276" t="n">
         <v>74.34999999999999</v>
       </c>
       <c r="E276" t="n">
-        <v>2024</v>
+        <v>234.3004147</v>
       </c>
       <c r="F276" t="n">
-        <v>11</v>
+        <v>5.475040258</v>
       </c>
     </row>
     <row r="277">
@@ -5969,19 +5969,19 @@
         <v>45627</v>
       </c>
       <c r="B277" t="n">
-        <v>232.98880929407</v>
+        <v>2024</v>
       </c>
       <c r="C277" t="n">
-        <v>227.981714585387</v>
+        <v>12</v>
       </c>
       <c r="D277" t="n">
         <v>73.86</v>
       </c>
       <c r="E277" t="n">
-        <v>2024</v>
+        <v>232.9888093</v>
       </c>
       <c r="F277" t="n">
-        <v>12</v>
+        <v>5.223478729</v>
       </c>
     </row>
     <row r="278">
@@ -5989,19 +5989,19 @@
         <v>45658</v>
       </c>
       <c r="B278" t="n">
-        <v>230.604072249095</v>
+        <v>2025</v>
       </c>
       <c r="C278" t="n">
-        <v>228.346459642452</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
         <v>79.27</v>
       </c>
       <c r="E278" t="n">
-        <v>2025</v>
+        <v>230.6040722</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>4.258760108</v>
       </c>
     </row>
     <row r="279">
@@ -6009,19 +6009,19 @@
         <v>45689</v>
       </c>
       <c r="B279" t="n">
-        <v>229.530940578856</v>
+        <v>2025</v>
       </c>
       <c r="C279" t="n">
-        <v>231.337947051496</v>
+        <v>2</v>
       </c>
       <c r="D279" t="n">
         <v>75.44</v>
       </c>
       <c r="E279" t="n">
-        <v>2025</v>
+        <v>229.5309406</v>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3.606027987</v>
       </c>
     </row>
     <row r="280">
@@ -6029,19 +6029,19 @@
         <v>45717</v>
       </c>
       <c r="B280" t="n">
-        <v>228.934756317612</v>
+        <v>2025</v>
       </c>
       <c r="C280" t="n">
-        <v>232.633498376547</v>
+        <v>3</v>
       </c>
       <c r="D280" t="n">
         <v>72.73</v>
       </c>
       <c r="E280" t="n">
-        <v>2025</v>
+        <v>228.9347563</v>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>3.336921421</v>
       </c>
     </row>
     <row r="281">
@@ -6049,19 +6049,19 @@
         <v>45748</v>
       </c>
       <c r="B281" t="n">
-        <v>229.650177431105</v>
+        <v>2025</v>
       </c>
       <c r="C281" t="n">
-        <v>233.633978656313</v>
+        <v>4</v>
       </c>
       <c r="D281" t="n">
         <v>68.13</v>
       </c>
       <c r="E281" t="n">
-        <v>2025</v>
+        <v>229.6501774</v>
       </c>
       <c r="F281" t="n">
-        <v>4</v>
+        <v>3.160149973</v>
       </c>
     </row>
     <row r="282">
@@ -6069,19 +6069,19 @@
         <v>45778</v>
       </c>
       <c r="B282" t="n">
-        <v>230.1271248401</v>
+        <v>2025</v>
       </c>
       <c r="C282" t="n">
-        <v>234.241458980228</v>
+        <v>5</v>
       </c>
       <c r="D282" t="n">
         <v>64.45</v>
       </c>
       <c r="E282" t="n">
-        <v>2025</v>
+        <v>230.1271248</v>
       </c>
       <c r="F282" t="n">
-        <v>5</v>
+        <v>2.823654768</v>
       </c>
     </row>
     <row r="283">
@@ -6089,19 +6089,19 @@
         <v>45809</v>
       </c>
       <c r="B283" t="n">
-        <v>231.557967067085</v>
+        <v>2025</v>
       </c>
       <c r="C283" t="n">
-        <v>234.803667250405</v>
+        <v>6</v>
       </c>
       <c r="D283" t="n">
         <v>71.44</v>
       </c>
       <c r="E283" t="n">
-        <v>2025</v>
+        <v>231.5579671</v>
       </c>
       <c r="F283" t="n">
-        <v>6</v>
+        <v>2.103049422</v>
       </c>
     </row>
     <row r="284">
@@ -6109,19 +6109,59 @@
         <v>45839</v>
       </c>
       <c r="B284" t="n">
-        <v>233.704322</v>
+        <v>2025</v>
       </c>
       <c r="C284" t="n">
-        <v>235.414037279877</v>
+        <v>7</v>
       </c>
       <c r="D284" t="n">
         <v>71.04000000000001</v>
       </c>
       <c r="E284" t="n">
+        <v>233.8234673</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1.606217617</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B285" t="n">
         <v>2025</v>
       </c>
-      <c r="F284" t="n">
-        <v>7</v>
+      <c r="C285" t="n">
+        <v>8</v>
+      </c>
+      <c r="D285" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="E285" t="n">
+        <v>234.8965989</v>
+      </c>
+      <c r="F285" t="n">
+        <v>2.07253886</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C286" t="n">
+        <v>9</v>
+      </c>
+      <c r="D286" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="E286" t="n">
+        <v>235.1350726</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1.544799176</v>
       </c>
     </row>
   </sheetData>
